--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:I37" headerRowCount="1">
-  <autoFilter ref="A1:I37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:I38" headerRowCount="1">
+  <autoFilter ref="A1:I38"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1837,31 +1837,35 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 18:49:48</t>
         </is>
       </c>
       <c r="E36" s="1" t="n">
-        <v>59.37</v>
+        <v>122.76</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Flor FST15</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>This version has all the features</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
+          <t>images/UP_02_v2_0_imagem.png</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -1874,30 +1878,67 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>UpperSupport Version</t>
+          <t>UP_03</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>2026-10-12 15:47:39</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
+        <v>59.37</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Flor FST15</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>UpperSupport Version</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:47:39</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>images\UpperSupport Version_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="E36" s="1" t="n">
-        <v>122.76</v>
+        <v>116.27</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:I38" headerRowCount="1">
-  <autoFilter ref="A1:I38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:I44" headerRowCount="1">
+  <autoFilter ref="A1:I44"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -1650,56 +1650,55 @@
         </is>
       </c>
       <c r="E31" s="1" t="n">
+        <v>1049.81</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To make a baseline </t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_01_vFST15_20261014_003807.png</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1758, "LC2": 0.2702, "LC3": 0.3631, "LC4": 0.285, "LC5": 0.2541, "LC6": 0.3201, "LC7": 0.3598, "LC8": 0.0835, "LC9": 0.0835}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>UP_01</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:56:06</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="n">
         <v>973.05</v>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The new upper support design
 </t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>images\UP_01_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>{"LC1": 0.2955, "LC2": 0.4246, "LC3": 0.3381, "LC4": 0.4214, "LC5": 0.4229, "LC6": 0.3262, "LC7": 0.3574, "LC8": 0.0835, "LC9": 0.0835}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>UP_01</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-12 15:56:06</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>973.05</v>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The new upper support design
-</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Transmission: v1.2
@@ -1763,34 +1762,42 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>2.0 (without supports)</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 20:33:44</t>
         </is>
       </c>
       <c r="E34" s="1" t="n">
-        <v>114.52</v>
+        <v>532.01</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+          <t>For comparing weight before adding the suspension supports with the FST15 design</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>images/UP_01_v2_0 (without supports)_20261013_203344.png</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.0, "LC2": 0.0, "LC3": 0.0, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0, "LC9": 0.0}</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1800,34 +1807,42 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>FST15 (without supports)</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-13 20:35:55</t>
         </is>
       </c>
       <c r="E35" s="1" t="n">
-        <v>101.15</v>
+        <v>677.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
+          <t>To make a baseline without the supports but with otimization of the transmission area</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: vFST15</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>images/UP_01_vFST15 (without supports)_20261013_203555.png</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.0, "LC2": 0.0, "LC3": 0.0, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0, "LC9": 0.0}</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1837,7 +1852,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1847,15 +1862,15 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 18:49:48</t>
+          <t>2026-10-14 00:25:37</t>
         </is>
       </c>
       <c r="E36" s="1" t="n">
-        <v>116.27</v>
+        <v>1029.86</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>This version has all the features</t>
+          <t xml:space="preserve">To make a baseline </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1865,10 +1880,14 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0_imagem.png</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>images/UP_01_v2_0_20261014_002537.png</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.2451, "LC2": 0.231, "LC3": 0.4058, "LC4": 0.2989, "LC5": 0.2604, "LC6": 0.3203, "LC7": 0.367, "LC8": 0.0841, "LC9": 0.0841}</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1878,34 +1897,38 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>2.0.1</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-14 01:22:40</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>59.37</v>
+        <v>1029.86</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Flor FST15</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">To make a baseline </t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1594, "LC2": 0.2208, "LC3": 0.4183, "LC4": 0.3058, "LC5": 0.2652, "LC6": 0.322, "LC7": 0.3708, "LC8": 0.0849, "LC9": 0.0849}</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1915,30 +1938,261 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>UpperSupport Version</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>2026-10-12 15:47:39</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
+        <v>114.52</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Upright Lid FST15</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
+          <t>images\UP_02_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:49:19</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_02_v1_imagem.png</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>FST15 (with all features)</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:39:47</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>120.04</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>2.0 (with all features)</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:48:17</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Flor FST15</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>UpperSupport Version</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:47:39</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">With all the features
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
           <t>images\UpperSupport Version_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>UpperSupport Version</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:22:29</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>images/UpperSupport Version_v2_0_20261014_002229.png</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:I44" headerRowCount="1">
-  <autoFilter ref="A1:I44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:I45" headerRowCount="1">
+  <autoFilter ref="A1:I45"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1938,34 +1938,42 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-14 11:33:53</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>114.52</v>
+        <v>1029.86</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>same supports as v2.0 but with bigger fillets in the pillars</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
+          <t>images/UP_01_v2_1_20261014_113714.png</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1469, "LC2": 0.1923, "LC3": 0.3673, "LC4": 0.275, "LC5": 0.2377, "LC6": 0.2701, "LC7": 0.3129, "LC8": 0.0801, "LC9": 0.0801}</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1980,26 +1988,26 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>101.15</v>
+        <v>114.52</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
+          <t>Upright Lid FST15</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
+          <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2017,26 +2025,26 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-06 18:49:19</t>
         </is>
       </c>
       <c r="E40" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+        <v>101.15</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+          <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2054,22 +2062,18 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>2.0 (with all features)</t>
+          <t>FST15 (with all features)</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:48:17</t>
+          <t>2026-10-13 20:39:47</t>
         </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>116.27</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Corrected dimensions and features</t>
-        </is>
-      </c>
+        <v>120.04</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2090,31 +2094,35 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>2.0 (with all features)</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 20:48:17</t>
         </is>
       </c>
       <c r="E42" s="1" t="n">
-        <v>59.37</v>
+        <v>116.27</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Flor FST15</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2127,72 +2135,109 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Flor FST15</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>2026-10-12 15:47:39</t>
         </is>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E44" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">With all the features
 </t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>images\UpperSupport Version_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 00:22:29</t>
         </is>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E45" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>images/UpperSupport Version_v2_0_20261014_002229.png</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,9 +131,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:I45" headerRowCount="1">
-  <autoFilter ref="A1:I45"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:J46" headerRowCount="1">
+  <autoFilter ref="A1:J46"/>
+  <tableColumns count="10">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
     <tableColumn id="3" name="Version"/>
@@ -143,6 +143,7 @@
     <tableColumn id="7" name="Constraints"/>
     <tableColumn id="8" name="Image Path"/>
     <tableColumn id="9" name="Stiffness Data"/>
+    <tableColumn id="10" name="LC Images"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -449,6 +450,7 @@
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +497,11 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Stiffness Data</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>LC Images</t>
         </is>
       </c>
     </row>
@@ -546,6 +553,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -588,6 +596,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,6 +643,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -680,6 +690,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -717,6 +728,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -755,6 +767,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -792,6 +805,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -829,6 +843,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -867,6 +882,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -905,6 +921,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -943,6 +960,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -981,6 +999,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1019,6 +1038,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1057,6 +1077,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1095,6 +1116,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1133,6 +1155,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1171,6 +1194,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1209,6 +1233,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1247,6 +1272,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1285,6 +1311,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1323,6 +1350,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1361,6 +1389,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1399,6 +1428,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1437,6 +1467,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1475,6 +1506,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1513,6 +1545,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1551,6 +1584,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1589,6 +1623,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1627,6 +1662,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1668,6 +1704,7 @@
           <t>{"LC1": 0.1758, "LC2": 0.2702, "LC3": 0.3631, "LC4": 0.285, "LC5": 0.2541, "LC6": 0.3201, "LC7": 0.3598, "LC8": 0.0835, "LC9": 0.0835}</t>
         </is>
       </c>
+      <c r="J31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1711,6 +1748,7 @@
           <t>{"LC1": 0.3429, "LC2": 0.3914, "LC3": 0.7797, "LC4": 0.5463, "LC5": 0.4658, "LC6": 0.6519, "LC7": 0.7425, "LC8": 0.1437, "LC9": 0.1437}</t>
         </is>
       </c>
+      <c r="J32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1753,6 +1791,7 @@
           <t>{"LC1": 0.2032, "LC2": 0.2119, "LC3": 0.4325, "LC4": 0.331, "LC5": 0.2905, "LC6": 0.3288, "LC7": 0.3826, "LC8": 0.0883, "LC9": 0.0883}</t>
         </is>
       </c>
+      <c r="J33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1798,6 +1837,7 @@
           <t>{"LC1": 0.0, "LC2": 0.0, "LC3": 0.0, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0, "LC9": 0.0}</t>
         </is>
       </c>
+      <c r="J34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1843,6 +1883,7 @@
           <t>{"LC1": 0.0, "LC2": 0.0, "LC3": 0.0, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0, "LC9": 0.0}</t>
         </is>
       </c>
+      <c r="J35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1888,6 +1929,7 @@
           <t>{"LC1": 0.2451, "LC2": 0.231, "LC3": 0.4058, "LC4": 0.2989, "LC5": 0.2604, "LC6": 0.3203, "LC7": 0.367, "LC8": 0.0841, "LC9": 0.0841}</t>
         </is>
       </c>
+      <c r="J36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1929,6 +1971,7 @@
           <t>{"LC1": 0.1594, "LC2": 0.2208, "LC3": 0.4183, "LC4": 0.3058, "LC5": 0.2652, "LC6": 0.322, "LC7": 0.3708, "LC8": 0.0849, "LC9": 0.0849}</t>
         </is>
       </c>
+      <c r="J37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1974,6 +2017,7 @@
           <t>{"LC1": 0.1469, "LC2": 0.1923, "LC3": 0.3673, "LC4": 0.275, "LC5": 0.2377, "LC6": 0.2701, "LC7": 0.3129, "LC8": 0.0801, "LC9": 0.0801}</t>
         </is>
       </c>
+      <c r="J38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1983,34 +2027,47 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-14 19:16:18</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>114.52</v>
+        <v>1022.6</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t>New try for the pillars and simpler uppersupports of v2.0</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>images/UP_01_v3_0_20261014_191617.png</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1597, "LC2": 0.2183, "LC3": 0.4255, "LC4": 0.3094, "LC5": 0.2667, "LC6": 0.3255, "LC7": 0.3747, "LC8": 0.0881, "LC9": 0.0881}</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v3_0_LC1_20261014_191617.png", "LC2": "images/UP_01_v3_0_LC2_20261014_191617.png", "LC3": "images/UP_01_v3_0_LC3_20261014_191617.png", "LC8": "images/UP_01_v3_0_LC8_20261014_191617.png", "LC4": "images/UP_01_v3_0_LC4_20261014_192056.png", "LC5": "images/UP_01_v3_0_LC5_20261014_192056.png", "LC6": "images/UP_01_v3_0_LC6_20261014_192056.png", "LC7": "images/UP_01_v3_0_LC7_20261014_192056.png"}</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -2025,29 +2082,30 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E40" s="1" t="n">
-        <v>101.15</v>
+        <v>114.52</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
+          <t>Upright Lid FST15</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
+          <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -2062,29 +2120,30 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-06 18:49:19</t>
         </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+        <v>101.15</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+          <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -2099,22 +2158,18 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>2.0 (with all features)</t>
+          <t>FST15 (with all features)</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:48:17</t>
+          <t>2026-10-13 20:39:47</t>
         </is>
       </c>
       <c r="E42" s="1" t="n">
-        <v>116.27</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Corrected dimensions and features</t>
-        </is>
-      </c>
+        <v>120.04</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
@@ -2122,10 +2177,11 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -2135,34 +2191,39 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>2.0 (with all features)</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 20:48:17</t>
         </is>
       </c>
       <c r="E43" s="1" t="n">
-        <v>59.37</v>
+        <v>116.27</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Flor FST15</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -2172,72 +2233,112 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Flor FST15</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>2026-10-12 15:47:39</t>
         </is>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E45" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">With all the features
 </t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>images\UpperSupport Version_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 00:22:29</t>
         </is>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E46" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>images/UpperSupport Version_v2_0_20261014_002229.png</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:J46" headerRowCount="1">
-  <autoFilter ref="A1:J46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:J49" headerRowCount="1">
+  <autoFilter ref="A1:J49"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2077,35 +2077,48 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-15 10:25:28</t>
         </is>
       </c>
       <c r="E40" s="1" t="n">
-        <v>114.52</v>
+        <v>1153.17</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
+          <t>Bigger fillets on the pillars</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t>images/UP_01_v3_1_20261015_102528.png</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1248, "LC2": 0.1625, "LC3": 0.3052, "LC4": 0.2234, "LC5": 0.1917, "LC6": 0.2315, "LC7": 0.2664, "LC8": 0.0648, "LC9": 0.0648}</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v3_1_LC1_20261015_103709.png", "LC2": "images/UP_01_v3_1_LC2_20261015_103709.png", "LC3": "images/UP_01_v3_1_LC3_20261015_103709.png", "LC4": "images/UP_01_v3_1_LC4_20261015_103710.png", "LC5": "images/UP_01_v3_1_LC5_20261015_103710.png", "LC6": "images/UP_01_v3_1_LC6_20261015_103710.png", "LC7": "images/UP_01_v3_1_LC7_20261015_103710.png", "LC8": "images/UP_01_v3_1_LC8_20261015_103710.png", "LC9": "images/UP_01_v3_1_LC9_20261015_103710.png"}</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -2115,35 +2128,48 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>FST15 (1 body)</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-15 10:30:42</t>
         </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>101.15</v>
+        <v>1170.2</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
+          <t>The baseline with one body. The fastest way to iterate</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: vFST15
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
+          <t>images/UP_01_vFST15 (1 body)_20261015_103042.png</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1664, "LC2": 0.2509, "LC3": 0.3437, "LC4": 0.2647, "LC5": 0.2364, "LC6": 0.2997, "LC7": 0.3382, "LC8": 0.076, "LC9": 0.076}</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_vFST15 (1 body)_LC1_20261015_103042.png", "LC2": "images/UP_01_vFST15 (1 body)_LC2_20261015_103042.png", "LC3": "images/UP_01_vFST15 (1 body)_LC3_20261015_103042.png", "LC4": "images/UP_01_vFST15 (1 body)_LC4_20261015_103042.png", "LC5": "images/UP_01_vFST15 (1 body)_LC5_20261015_103042.png", "LC6": "images/UP_01_vFST15 (1 body)_LC6_20261015_103042.png", "LC7": "images/UP_01_vFST15 (1 body)_LC7_20261015_103042.png", "LC8": "images/UP_01_vFST15 (1 body)_LC8_20261015_103042.png", "LC9": "images/UP_01_vFST15 (1 body)_LC9_20261015_103042.png"}</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -2153,35 +2179,49 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>2.0 (1 body)</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-15 10:51:55</t>
         </is>
       </c>
       <c r="E42" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sanity Check on the baseline
+</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Transmission: v2.0</t>
+          <t>Transmission: v2.0
+Bodies: 1</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
+          <t>images/UP_01_v2_0 (1 body)_20261015_105155.png</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1484, "LC2": 0.2071, "LC3": 0.3885, "LC4": 0.2854, "LC5": 0.2487, "LC6": 0.2998, "LC7": 0.3459, "LC8": 0.0788, "LC9": 0.0788}</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -2196,30 +2236,26 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>2.0 (with all features)</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:48:17</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E43" s="1" t="n">
-        <v>116.27</v>
+        <v>114.52</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Corrected dimensions and features</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+          <t>Upright Lid FST15</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+          <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2233,31 +2269,31 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-06 18:49:19</t>
         </is>
       </c>
       <c r="E44" s="1" t="n">
-        <v>59.37</v>
+        <v>101.15</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Flor FST15</t>
+          <t>Due to the less height is lighter</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
+          <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2271,74 +2307,192 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>FST15 (with all features)</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:39:47</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>120.04</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>2.0 (with all features)</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:48:17</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Flor FST15</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>2026-10-12 15:47:39</t>
         </is>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E48" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">With all the features
 </t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>images\UpperSupport Version_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 00:22:29</t>
         </is>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E49" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>images/UpperSupport Version_v2_0_20261014_002229.png</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:J49" headerRowCount="1">
-  <autoFilter ref="A1:J49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:J54" headerRowCount="1">
+  <autoFilter ref="A1:J54"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2231,35 +2231,49 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>3.1 (without supports)</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-15 11:17:35</t>
         </is>
       </c>
       <c r="E43" s="1" t="n">
-        <v>114.52</v>
+        <v>693.88</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">For comparison without supports with FST15
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
+          <t>images/UP_01_v3_1 (without supports)_20261015_111735.png</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1484, "LC2": 0.2071, "LC3": 0.3885, "LC4": 0.2854, "LC5": 0.2487, "LC6": 0.2998, "LC7": 0.3459, "LC8": 0.0788, "LC9": 0.0788}</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -2269,35 +2283,49 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-15 11:54:58</t>
         </is>
       </c>
       <c r="E44" s="1" t="n">
-        <v>101.15</v>
+        <v>1149.1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Smaller fillet on the upright
+</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
+          <t>images/UP_01_v3_2_20261015_115458.png</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1311, "LC2": 0.1734, "LC3": 0.3176, "LC4": 0.2332, "LC5": 0.2011, "LC6": 0.2437, "LC7": 0.2799, "LC8": 0.0669, "LC9": 0.0669}</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v3_2_LC1_20261015_115458.png", "LC2": "images/UP_01_v3_2_LC2_20261015_115458.png", "LC3": "images/UP_01_v3_2_LC3_20261015_115458.png", "LC4": "images/UP_01_v3_2_LC4_20261015_115458.png", "LC5": "images/UP_01_v3_2_LC5_20261015_115458.png", "LC6": "images/UP_01_v3_2_LC6_20261015_115458.png", "LC7": "images/UP_01_v3_2_LC7_20261015_115458.png", "LC8": "images/UP_01_v3_2_LC8_20261015_115746.png", "LC9": "images/UP_01_v3_2_LC9_20261015_115746.png"}</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -2307,35 +2335,49 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-15 16:05:42</t>
         </is>
       </c>
       <c r="E45" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
+        <v>1145.42</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Make sure the clearences were obtained and had to reduce the fillets on the upright
+</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Transmission: v2.0</t>
+          <t>Transmission: v2.0
+Bodies: 1</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
+          <t>images/UP_01_v3_3_20261015_160541.png</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1443, "LC2": 0.1952, "LC3": 0.3579, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": 0.0738, "LC9": 0.0738}</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v3_3_LC1_20261015_160541.png", "LC2": "images/UP_01_v3_3_LC2_20261015_160541.png", "LC3": "images/UP_01_v3_3_LC3_20261015_160541.png", "LC8": "images/UP_01_v3_3_LC8_20261015_160541.png", "LC9": "images/UP_01_v3_3_LC9_20261015_160542.png"}</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -2345,39 +2387,49 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>2.0 (with all features)</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:48:17</t>
+          <t>2026-10-15 16:21:56</t>
         </is>
       </c>
       <c r="E46" s="1" t="n">
-        <v>116.27</v>
+        <v>1146.28</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Corrected dimensions and features</t>
+          <t xml:space="preserve">The 3.3 didint give the results i wanted so i changed a bit the low fillet to see if improves stiffness
+</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Transmission: v2.0</t>
+          <t>Transmission: v2.0
+Bodies: 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
+          <t>images/UP_01_v3_3_1_20261015_162156.png</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1443, "LC2": 0.1952, "LC3": 0.3579, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": 0.0738, "LC9": 0.0738}</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -2387,35 +2439,49 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-15 16:26:11</t>
         </is>
       </c>
       <c r="E47" s="1" t="n">
-        <v>59.37</v>
+        <v>1146.28</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Flor FST15</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
+          <t xml:space="preserve">The 3.3 didint give the results i wanted so i changed a bit the low fillet to see if improves stiffness
+</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
+          <t>images/UP_01_v3_3_1_20261015_162611.png</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1429, "LC2": 0.1936, "LC3": 0.3532, "LC4": 0.2577, "LC5": 0.2236, "LC6": 0.2743, "LC7": 0.3151, "LC8": 0.0728, "LC9": 0.0738}</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v3_3_1_LC1_20261015_162611.png", "LC2": "images/UP_01_v3_3_1_LC2_20261015_162611.png", "LC3": "images/UP_01_v3_3_1_LC3_20261015_162611.png", "LC8": "images/UP_01_v3_3_1_LC8_20261015_162611.png", "LC9": "images/UP_01_v3_3_1_LC9_20261015_162611.png"}</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -2425,74 +2491,268 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>114.52</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Upright Lid FST15</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_02_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:49:19</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_02_v1_imagem.png</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>FST15 (with all features)</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:39:47</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>120.04</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>2.0 (with all features)</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:48:17</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Flor FST15</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="D53" s="1" t="inlineStr">
         <is>
           <t>2026-10-12 15:47:39</t>
         </is>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E53" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">With all the features
 </t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>images\UpperSupport Version_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
+      <c r="B54" s="1" t="inlineStr">
         <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="D54" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 00:22:29</t>
         </is>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E54" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>images/UpperSupport Version_v2_0_20261014_002229.png</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -1144,16 +1144,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Schaeffler Bearing: 61816
-Datasheet: 61816</t>
+          <t xml:space="preserve">Schaeffler Bearing: 61816  
+Datasheet: https://medias.schaeffler.es/pt/produto/rotary/rolamentos%2c-mancais-de-deslizamento/rolamentos-de-esferas/rolamentos-rigidos-de-esferas/61816/p/2893831#Product%20Information </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Inner D (mm): 80 | Dynamic Load Cr (kN): 13.8 | Static Load C0r (kN): 13.8 | Speed Limit (rpm): 9400</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+          <t>d (Diâmetro do furo): 80 mm
+D (Diâmetro externo): 100 mm
+B (Width / Largura): 10 mm
+Cr (Capacidade de carga dinâmica, radial): 13.800 N
+C0r (Capacidade de carga estática, radial): 13.800 N
+Cur (Limite de carga por fadiga, radial): 930 N
+nG (Velocidade limite): 9.400 1/min
+n_ref (Velocidade nominal): 4.600 1/min
+da min (Diâmetro mín. ressalto do veio): 83,2 mm
+Da max (Diâmetro máx. ressalto da casquilho): 96,8 mm
+ra max (Raio máximo da ranhura): 0,6 mm
+rmin (Minimum chamfer dimension): 0,6 mm
+D1 (Diâmetro do ressalto do anel exterior): 93,57 mm
+d1 (Diâmetro do ressalto do anel interior): 86,6 mm
+Tmin (Temperatura de operação min.): -30 °C
+Tmax (Temperatura de operação max.): 150 °C
+f0 (Fator de cálculo): 16</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>images/61816_vOEM_20261017_103218.png</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
     </row>

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,14 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -128,25 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:J54" headerRowCount="1">
-  <autoFilter ref="A1:J54"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="Subassembly"/>
-    <tableColumn id="2" name="Part Name"/>
-    <tableColumn id="3" name="Version"/>
-    <tableColumn id="4" name="Date"/>
-    <tableColumn id="5" name="Weight (g)"/>
-    <tableColumn id="6" name="Description"/>
-    <tableColumn id="7" name="Constraints"/>
-    <tableColumn id="8" name="Image Path"/>
-    <tableColumn id="9" name="Stiffness Data"/>
-    <tableColumn id="10" name="LC Images"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -438,20 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -486,7 +449,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Constraints</t>
+          <t>Specifications</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -504,38 +467,48 @@
           <t>LC Images</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Tolerancing Data</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2026-10-06 14:09:09</t>
         </is>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">This is a simplified transmission to make iteractions easier
 </t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Center Distance: 32mm
 Big Planet Diameter: 45.6mm
@@ -547,40 +520,42 @@
 Axles Diameter: 7mm</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>images\TD_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-10-06 14:50:41</t>
         </is>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Center Distance: 32.5
 Big Planet Diameter: 49.1241
@@ -594,40 +569,42 @@
 sun gear diameter: 19.0199</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2026-10-06 14:52:08</t>
         </is>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Its the rounded number of version v1.1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Center Distance: 32.5
 Big Planet Diameter: 49.5
@@ -641,40 +618,42 @@
 Sun Gear Diameter: 19.5</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2026-10-12 11:01:13</t>
         </is>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">New version to try </t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Center Distance: 30
 Big Planet Diameter: 46.5
@@ -688,2096 +667,1723 @@
 Sun Gear Diameter: 16</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>HB_01</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" t="n">
         <v>654.66</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>With equal features</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>images\HB_01_vFST15_imagem.png</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Inner Bearing Shaft Seat (d=80mm)", "Nominal (mm)": "80", "Fit / Tolerance": "k5 (+0.009 / +0.002 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground, mates with 61816 bearing)"}, {"Interface / Feature": "Seal Running Land / Counterface (d1=85mm)", "Nominal (mm)": "85", "Fit / Tolerance": "h11 (0 / -0.220 mm)", "Roughness / Notes": "Ra = 0.2 - 0.5 um (plunge ground, zero lead)"}, {"Interface / Feature": "Wheel Stud Pitch Circle (PCD)", "Nominal (mm)": "4x PCD 100", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Runout &lt; 0.02 mm (wheel rim pilot)"}, {"Interface / Feature": "Brake Rotor Mounting Face", "Nominal (mm)": "Flatness", "Fit / Tolerance": "Axial runout &lt; 0.015 mm", "Roughness / Notes": "Ra &lt;= 0.8 um (prevents brake shudder)"}]</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>HB_01</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>2026-10-06 18:38:55</t>
         </is>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" t="n">
         <v>609.24</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">68 mm of height compared to 77mm in FST15
 </t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>images\HB_01_v1_imagem.png</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Inner Bearing Shaft Seat (d=80mm)", "Nominal (mm)": "80", "Fit / Tolerance": "k5 (+0.009 / +0.002 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground, mates with 61816 bearing)"}, {"Interface / Feature": "Seal Running Land / Counterface (d1=85mm)", "Nominal (mm)": "85", "Fit / Tolerance": "h11 (0 / -0.220 mm)", "Roughness / Notes": "Ra = 0.2 - 0.5 um (plunge ground, zero lead)"}, {"Interface / Feature": "Wheel Stud Pitch Circle (PCD)", "Nominal (mm)": "4x PCD 100", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Runout &lt; 0.02 mm (wheel rim pilot)"}, {"Interface / Feature": "Brake Rotor Mounting Face", "Nominal (mm)": "Flatness", "Fit / Tolerance": "Axial runout &lt; 0.015 mm", "Roughness / Notes": "Ra &lt;= 0.8 um (prevents brake shudder)"}]</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>HB_01</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026-10-07 13:36:53</t>
         </is>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" t="n">
         <v>596.3200000000001</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>the difference to 1.0 is due to missing the interface for the sleeve</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>images\HB_01_v1_1_imagem.png</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Inner Bearing Shaft Seat (d=80mm)", "Nominal (mm)": "80", "Fit / Tolerance": "k5 (+0.009 / +0.002 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground, mates with 61816 bearing)"}, {"Interface / Feature": "Seal Running Land / Counterface (d1=85mm)", "Nominal (mm)": "85", "Fit / Tolerance": "h11 (0 / -0.220 mm)", "Roughness / Notes": "Ra = 0.2 - 0.5 um (plunge ground, zero lead)"}, {"Interface / Feature": "Wheel Stud Pitch Circle (PCD)", "Nominal (mm)": "4x PCD 100", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Runout &lt; 0.02 mm (wheel rim pilot)"}, {"Interface / Feature": "Brake Rotor Mounting Face", "Nominal (mm)": "Flatness", "Fit / Tolerance": "Axial runout &lt; 0.015 mm", "Roughness / Notes": "Ra &lt;= 0.8 um (prevents brake shudder)"}]</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HB_02</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:28:41</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Retaining Nut Thread / Bore", "Nominal (mm)": "M75x1.5", "Fit / Tolerance": "6H/6g", "Roughness / Notes": "Ra &lt;= 1.6 um (spindle axial retention)"}]</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>HB_07</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2026-10-06 18:44:16</t>
         </is>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E10" t="n">
         <v>6.78</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2mm to ensure no contact between the bearing and the seal</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>images\HB_07_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Spacer Inner Bore", "Nominal (mm)": "80.5", "Fit / Tolerance": "+0.2 / 0 mm", "Roughness / Notes": "Ra &lt;= 3.2 um (clears 80mm spindle)"}, {"Interface / Feature": "Spacer Length (Face-to-Face)", "Nominal (mm)": "12.0", "Fit / Tolerance": "+/- 0.02 mm", "Roughness / Notes": "Parallelism &lt; 0.005 mm (sets bearing preload)"}]</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>100X115X9 HMSA10 V1</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>61815</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SKF Seal: 100X115X9 HMSA10 V1
-Datasheet: 100X115X9 </t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 100 | Outer D Min (mm): 115 | Width Min (mm): 8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>105X130X12 HMSA10 V</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>SKF Seal: 105X130X12 HMSA10 V
-Datasheet: 105X130X12</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 105 | Outer D Min (mm): 130 | Width Min (mm): 12</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>108X140X15 HMSA10 V</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>123</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>SKF Seal: 108X140X15 HMSA10 V
-Datasheet: 108X140X15</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 108 | Outer D Min (mm): 140 | Width Min (mm): 15</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>110X130X8 HMSA10 V1</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SKF Seal: 110X130X8 HMSA10 V1
-Datasheet: 110X130X8 </t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 110 | Outer D Min (mm): 130 | Width Min (mm): 8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>115X140X12 HMSA10 V</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SKF Seal: 115X140X12 HMSA10 V
-Datasheet: 115X140X12 </t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 115 | Outer D Min (mm): 140 | Width Min (mm): 12</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>120X140X12 HMSA10 V</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>SKF Seal: 120X140X12 HMSA10 V
-Datasheet: 120X140X12</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 120 | Outer D Min (mm): 140 | Width Min (mm): 12</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>61815</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="n">
+      <c r="E11" t="n">
         <v>149</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61815
 Datasheet: 61815</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Inner D (mm): 75 | Dynamic Load Cr (kN): 13.7 | Static Load C0r (kN): 13.4 | Speed Limit (rpm): 10000</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Shaft Seat (d=75mm)", "Nominal (mm)": "75", "Fit / Tolerance": "k5 (+0.009 / +0.002 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground)"}, {"Interface / Feature": "Housing Bore (D=95mm)", "Nominal (mm)": "95", "Fit / Tolerance": "H7 (+0.030 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um"}, {"Interface / Feature": "Shaft Shoulder (da min)", "Nominal (mm)": "78.2", "Fit / Tolerance": "da &gt;= 78.2 mm (h11)", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Housing Shoulder (Da max)", "Nominal (mm)": "91.8", "Fit / Tolerance": "Da &lt;= 91.8 mm (H11)", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Shaft Radial Runout", "Nominal (mm)": "75", "Fit / Tolerance": "IT4 (0.004 mm)", "Roughness / Notes": "Max permissible TIR"}]</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>61816</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E12" t="n">
         <v>157</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Schaeffler Bearing: 61816  
-Datasheet: https://medias.schaeffler.es/pt/produto/rotary/rolamentos%2c-mancais-de-deslizamento/rolamentos-de-esferas/rolamentos-rigidos-de-esferas/61816/p/2893831#Product%20Information </t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>d (Diâmetro do furo): 80 mm
-D (Diâmetro externo): 100 mm
-B (Width / Largura): 10 mm
-Cr (Capacidade de carga dinâmica, radial): 13.800 N
-C0r (Capacidade de carga estática, radial): 13.800 N
-Cur (Limite de carga por fadiga, radial): 930 N
-nG (Velocidade limite): 9.400 1/min
-n_ref (Velocidade nominal): 4.600 1/min
-da min (Diâmetro mín. ressalto do veio): 83,2 mm
-Da max (Diâmetro máx. ressalto da casquilho): 96,8 mm
-ra max (Raio máximo da ranhura): 0,6 mm
-rmin (Minimum chamfer dimension): 0,6 mm
-D1 (Diâmetro do ressalto do anel exterior): 93,57 mm
-d1 (Diâmetro do ressalto do anel interior): 86,6 mm
-Tmin (Temperatura de operação min.): -30 °C
-Tmax (Temperatura de operação max.): 150 °C
-f0 (Fator de cálculo): 16</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Baseline motor back plate iteration for FST15 carry-over.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>d (Bore diameter): 80 mm
+D (Outside diameter): 100 mm
+B (Width): 10 mm
+Cr (Basic dynamic load rating): 13.8 kN
+C0r (Basic static load rating): 13.8 kN
+Cur (Fatigue load limit): 0.93 kN
+nG (Limiting speed): 9400 rpm
+n_ref (Reference speed): 4600 rpm
+da min (Shaft abutment diameter): 83.2 mm
+Da max (Housing abutment diameter): 96.8 mm
+ra max (Fillet radius): 0.6 mm
+rmin (Min. chamfer dimension): 0.6 mm
+D1 (Outer ring shoulder diameter): 93.57 mm
+d1 (Inner ring shoulder diameter): 86.6 mm
+Tmin (Min. operating temp): -30 deg C
+Tmax (Max. operating temp): 150 deg C
+f0 (Calculation factor): 16</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>images/61816_vOEM_20261017_103218.png</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Shaft Seat (d=80mm)", "Nominal (mm)": "80", "Fit / Tolerance": "k5 (+0.009 / +0.002 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground)"}, {"Interface / Feature": "Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um"}, {"Interface / Feature": "Shaft Shoulder (da min)", "Nominal (mm)": "83.2", "Fit / Tolerance": "da &gt;= 83.2 mm (h11)", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Housing Shoulder (Da max)", "Nominal (mm)": "96.8", "Fit / Tolerance": "Da &lt;= 96.8 mm (H11)", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Shaft Radial Runout", "Nominal (mm)": "80", "Fit / Tolerance": "IT4 (0.004 mm)", "Roughness / Notes": "Max permissible TIR"}, {"Interface / Feature": "Shoulder Axial Runout", "Nominal (mm)": "83.2", "Fit / Tolerance": "IT4 (0.005 mm)", "Roughness / Notes": "Perpendicularity to axis"}]</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>61817</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>71815-TN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>270</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Schaeffler Bearing: 61817
-Datasheet: 61817</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 85 | Dynamic Load Cr (kN): 20.4 | Static Load C0r (kN): 19.8 | Speed Limit (rpm): 8500</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>61818</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>287</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Schaeffler Bearing: 61818
-Datasheet: 61818</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 90 | Dynamic Load Cr (kN): 20.7 | Static Load C0r (kN): 20.6 | Speed Limit (rpm): 8100</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>61819</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>301</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Schaeffler Bearing: 61819
-Datasheet: 61819</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 95 | Dynamic Load Cr (kN): 21.0 | Static Load C0r (kN): 21.3 | Speed Limit (rpm): 7700</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>61820</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>315</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Schaeffler Bearing: 61820
-Datasheet: 61820</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 100 | Dynamic Load Cr (kN): 21.3 | Static Load C0r (kN): 22.1 | Speed Limit (rpm): 7400</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>61821</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>330</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Schaeffler Bearing: 61821
-Datasheet: 61821</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 105 | Dynamic Load Cr (kN): 22.1 | Static Load C0r (kN): 23.6 | Speed Limit (rpm): 7100</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>61822</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>509</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Schaeffler Bearing: 61822
-Datasheet: 61822</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 110 | Dynamic Load Cr (kN): 30.0 | Static Load C0r (kN): 30.5 | Speed Limit (rpm): 6500</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>61824</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>551</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Schaeffler Bearing: 61824
-Datasheet: 61824</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 120 | Dynamic Load Cr (kN): 30.5 | Static Load C0r (kN): 33.0 | Speed Limit (rpm): 6100</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>71815-TN</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="n">
+      <c r="E13" t="n">
         <v>142</v>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 71815-TN
 Datasheet: 71815</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Inner D (mm): 75 | Dynamic Load Cr (kN): 16.2 | Static Load C0r (kN): 18.1 | Speed Limit (rpm): 8500</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Shaft Seat (d=75mm)", "Nominal (mm)": "75", "Fit / Tolerance": "m5 (+0.015 / +0.006 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground)"}, {"Interface / Feature": "Housing Bore (D=95mm)", "Nominal (mm)": "95", "Fit / Tolerance": "J7 (+0.018 / -0.012 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (light preload)"}, {"Interface / Feature": "Shaft Shoulder (da min)", "Nominal (mm)": "79.5", "Fit / Tolerance": "da &gt;= 79.5 mm", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Housing Shoulder (Da max)", "Nominal (mm)": "90.5", "Fit / Tolerance": "Da &lt;= 90.5 mm", "Roughness / Notes": "ra max = 0.6 mm"}]</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>71816-TN</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E14" t="n">
         <v>152</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 71816-TN
 Datasheet: 71816</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Inner D (mm): 80 | Dynamic Load Cr (kN): 16.5 | Static Load C0r (kN): 19.1 | Speed Limit (rpm): 8000</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Shaft Seat (d=80mm)", "Nominal (mm)": "80", "Fit / Tolerance": "m5 (+0.015 / +0.006 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground)"}, {"Interface / Feature": "Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "J7 (+0.018 / -0.012 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (light preload)"}, {"Interface / Feature": "Shaft Shoulder (da min)", "Nominal (mm)": "84.5", "Fit / Tolerance": "da &gt;= 84.5 mm", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Housing Shoulder (Da max)", "Nominal (mm)": "95.5", "Fit / Tolerance": "Da &lt;= 95.5 mm", "Roughness / Notes": "ra max = 0.6 mm"}]</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>71821-B-XL-TVP</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>85X100X9 HMSA10 V</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>316</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Schaeffler Bearing: 71821-B-XL-TVP
-Datasheet: 71821</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 105 | Dynamic Load Cr (kN): 24.7 | Static Load C0r (kN): 30.0 | Speed Limit (rpm): 6600</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="E15" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SKF Seal: 85X100X9 HMSA10 V
+Datasheet: https://www.skf.com/pt/products/industrial-seals/power-transmission-seals/radial-shaft-seals/general-industrial-applications/productid-85X100X9%20HMSA10%20V
+  85  ─────── Shaft diameter d1 = 85 mm (Upright sealing land)
+  100 ─────── Housing bore diameter D = 100 mm (Wheel hub internal seat)
+  9   ─────── Seal width b = 9 mm
+  HMS ─────── Rubber-covered outside diameter with corrugated/beaded OD profile
+  A   ─────── Integrated non-contacting auxiliary secondary dust lip
+  10  ─────── SKF Generation 10 hydrodynamic sealing lip with toroidal garter spring
+  V   ─────── Fluoroelastomer (FKM / Viton®) compound + Stainless Steel garter spring
+</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>d1 (Shaft diameter): 85 mm
+D (Housing bore diameter): 100 mm
+b (Seal width): 9 mm
+Seal Design: HMSA10
+Lip Material: Fluoroelastomer (FKM)
+Outer Diameter: Rubber-covered metal casing
+Auxiliary Dust Lip: Yes
+Standard: ISO 6194 / DIN 3760
+Operating Temp: -25 to 200 deg C
+Max Peripheral Speed: 31.2 m/s
+Max Rotational Speed: 7020 rpm
+Max Pressure Difference: 0.05 N/mm2</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>images/85X100X9 HMSA10 V_vOEM_20261017_104022.png</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Shaft Counterface (d1=85mm)", "Nominal (mm)": "85", "Fit / Tolerance": "h11 (0 / -0.220 mm)", "Roughness / Notes": "Ra = 0.2 - 0.5 um (plunge ground, zero lead)"}, {"Interface / Feature": "Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um"}, {"Interface / Feature": "Lead-in Chamfer", "Nominal (mm)": "15 to 30 deg", "Fit / Tolerance": "Length &gt;= 3 mm", "Roughness / Notes": "Edges rounded and burr-free"}, {"Interface / Feature": "Shaft Surface Hardness", "Nominal (mm)": "Contact zone", "Fit / Tolerance": "&gt;= 45 HRC (recommended 58 HRC)", "Roughness / Notes": "Case depth &gt;= 0.3 mm"}, {"Interface / Feature": "Dynamic Eccentricity / Runout", "Nominal (mm)": "7020 rpm", "Fit / Tolerance": "&lt; 0.05 mm", "Roughness / Notes": "Max permissible TIR"}]</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>85X100X9 HMSA10 V</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>95X110X9 HMSA10 V</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>SKF Seal: 85X100X9 HMSA10 V
-Datasheet: 85X100X9</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 85 | Outer D Min (mm): 100 | Width Min (mm): 9</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>90X105X9 HMSA10 V1</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SKF Seal: 90X105X9 HMSA10 V1
-Datasheet: 90X105X9 </t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 90 | Outer D Min (mm): 105 | Width Min (mm): 9</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>95X110X9 HMSA10 V</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="n">
+      <c r="E16" t="n">
         <v>44</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 95X110X9 HMSA10 V
 Datasheet: 95X110X9 </t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Inner D (mm): 95 | Outer D Min (mm): 110 | Width Min (mm): 9</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Shaft Counterface (d1=95mm)", "Nominal (mm)": "95", "Fit / Tolerance": "h11 (0 / -0.220 mm)", "Roughness / Notes": "Ra = 0.2 - 0.5 um (plunge ground, zero lead)"}, {"Interface / Feature": "Housing Bore (D=110mm)", "Nominal (mm)": "110", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um"}, {"Interface / Feature": "Lead-in Chamfer", "Nominal (mm)": "15 to 30 deg", "Fit / Tolerance": "Length &gt;= 3 mm", "Roughness / Notes": "Edges rounded and burr-free"}, {"Interface / Feature": "Dynamic Eccentricity / Runout", "Nominal (mm)": "7000 rpm", "Fit / Tolerance": "&lt; 0.05 mm", "Roughness / Notes": "Max permissible TIR"}]</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E17" t="n">
         <v>1049.81</v>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">To make a baseline </t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>images/UP_01_vFST15_20261014_003807.png</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>{"LC1": 0.1758, "LC2": 0.2702, "LC3": 0.3631, "LC4": 0.285, "LC5": 0.2541, "LC6": 0.3201, "LC7": 0.3598, "LC8": 0.0835, "LC9": 0.0835}</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2026-10-12 15:56:06</t>
         </is>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E18" t="n">
         <v>973.05</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">The new upper support design
 </t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Transmission: v1.2
 UpperSuport: v1.0</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>{"LC1": 0.3429, "LC2": 0.3914, "LC3": 0.7797, "LC4": 0.5463, "LC5": 0.4658, "LC6": 0.6519, "LC7": 0.7425, "LC8": 0.1437, "LC9": 0.1437}</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2026-10-12 16:58:21</t>
         </is>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E19" t="n">
         <v>996.61</v>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Maked the side walls solid</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Transmission: v1.2
 UpperSuport: v1.0</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>{"LC1": 0.2032, "LC2": 0.2119, "LC3": 0.4325, "LC4": 0.331, "LC5": 0.2905, "LC6": 0.3288, "LC7": 0.3826, "LC8": 0.0883, "LC9": 0.0883}</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>2.0 (without supports)</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2026-10-13 20:33:44</t>
         </is>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E20" t="n">
         <v>532.01</v>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>For comparing weight before adding the suspension supports with the FST15 design</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>images/UP_01_v2_0 (without supports)_20261013_203344.png</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>{"LC1": 0.0, "LC2": 0.0, "LC3": 0.0, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0, "LC9": 0.0}</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>FST15 (without supports)</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>2026-10-13 20:35:55</t>
         </is>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E21" t="n">
         <v>677.2</v>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>To make a baseline without the supports but with otimization of the transmission area</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Transmission: vFST15</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>images/UP_01_vFST15 (without supports)_20261013_203555.png</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>{"LC1": 0.0, "LC2": 0.0, "LC3": 0.0, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0, "LC9": 0.0}</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>2026-10-14 00:25:37</t>
         </is>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E22" t="n">
         <v>1029.86</v>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">To make a baseline </t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>images/UP_01_v2_0_20261014_002537.png</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>{"LC1": 0.2451, "LC2": 0.231, "LC3": 0.4058, "LC4": 0.2989, "LC5": 0.2604, "LC6": 0.3203, "LC7": 0.367, "LC8": 0.0841, "LC9": 0.0841}</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>2.0.1</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>2026-10-14 01:22:40</t>
         </is>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E23" t="n">
         <v>1029.86</v>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">To make a baseline </t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>{"LC1": 0.1594, "LC2": 0.2208, "LC3": 0.4183, "LC4": 0.3058, "LC5": 0.2652, "LC6": 0.322, "LC7": 0.3708, "LC8": 0.0849, "LC9": 0.0849}</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2026-10-14 11:33:53</t>
         </is>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E24" t="n">
         <v>1029.86</v>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>same supports as v2.0 but with bigger fillets in the pillars</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>images/UP_01_v2_1_20261014_113714.png</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>{"LC1": 0.1469, "LC2": 0.1923, "LC3": 0.3673, "LC4": 0.275, "LC5": 0.2377, "LC6": 0.2701, "LC7": 0.3129, "LC8": 0.0801, "LC9": 0.0801}</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2026-10-14 19:16:18</t>
         </is>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E25" t="n">
         <v>1022.6</v>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>New try for the pillars and simpler uppersupports of v2.0</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>images/UP_01_v3_0_20261014_191617.png</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>{"LC1": 0.1597, "LC2": 0.2183, "LC3": 0.4255, "LC4": 0.3094, "LC5": 0.2667, "LC6": 0.3255, "LC7": 0.3747, "LC8": 0.0881, "LC9": 0.0881}</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_0_LC1_20261014_191617.png", "LC2": "images/UP_01_v3_0_LC2_20261014_191617.png", "LC3": "images/UP_01_v3_0_LC3_20261014_191617.png", "LC8": "images/UP_01_v3_0_LC8_20261014_191617.png", "LC4": "images/UP_01_v3_0_LC4_20261014_192056.png", "LC5": "images/UP_01_v3_0_LC5_20261014_192056.png", "LC6": "images/UP_01_v3_0_LC6_20261014_192056.png", "LC7": "images/UP_01_v3_0_LC7_20261014_192056.png"}</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026-10-15 10:25:28</t>
         </is>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E26" t="n">
         <v>1153.17</v>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Bigger fillets on the pillars</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>images/UP_01_v3_1_20261015_102528.png</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>{"LC1": 0.1248, "LC2": 0.1625, "LC3": 0.3052, "LC4": 0.2234, "LC5": 0.1917, "LC6": 0.2315, "LC7": 0.2664, "LC8": 0.0648, "LC9": 0.0648}</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_1_LC1_20261015_103709.png", "LC2": "images/UP_01_v3_1_LC2_20261015_103709.png", "LC3": "images/UP_01_v3_1_LC3_20261015_103709.png", "LC4": "images/UP_01_v3_1_LC4_20261015_103710.png", "LC5": "images/UP_01_v3_1_LC5_20261015_103710.png", "LC6": "images/UP_01_v3_1_LC6_20261015_103710.png", "LC7": "images/UP_01_v3_1_LC7_20261015_103710.png", "LC8": "images/UP_01_v3_1_LC8_20261015_103710.png", "LC9": "images/UP_01_v3_1_LC9_20261015_103710.png"}</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>FST15 (1 body)</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>2026-10-15 10:30:42</t>
         </is>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E27" t="n">
         <v>1170.2</v>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>The baseline with one body. The fastest way to iterate</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Transmission: vFST15
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>images/UP_01_vFST15 (1 body)_20261015_103042.png</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>{"LC1": 0.1664, "LC2": 0.2509, "LC3": 0.3437, "LC4": 0.2647, "LC5": 0.2364, "LC6": 0.2997, "LC7": 0.3382, "LC8": 0.076, "LC9": 0.076}</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_vFST15 (1 body)_LC1_20261015_103042.png", "LC2": "images/UP_01_vFST15 (1 body)_LC2_20261015_103042.png", "LC3": "images/UP_01_vFST15 (1 body)_LC3_20261015_103042.png", "LC4": "images/UP_01_vFST15 (1 body)_LC4_20261015_103042.png", "LC5": "images/UP_01_vFST15 (1 body)_LC5_20261015_103042.png", "LC6": "images/UP_01_vFST15 (1 body)_LC6_20261015_103042.png", "LC7": "images/UP_01_vFST15 (1 body)_LC7_20261015_103042.png", "LC8": "images/UP_01_vFST15 (1 body)_LC8_20261015_103042.png", "LC9": "images/UP_01_vFST15 (1 body)_LC9_20261015_103042.png"}</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2.0 (1 body)</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2026-10-15 10:51:55</t>
         </is>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t xml:space="preserve">Sanity Check on the baseline
 </t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>images/UP_01_v2_0 (1 body)_20261015_105155.png</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>{"LC1": 0.1484, "LC2": 0.2071, "LC3": 0.3885, "LC4": 0.2854, "LC5": 0.2487, "LC6": 0.2998, "LC7": 0.3459, "LC8": 0.0788, "LC9": 0.0788}</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>3.1 (without supports)</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>2026-10-15 11:17:35</t>
         </is>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E29" t="n">
         <v>693.88</v>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t xml:space="preserve">For comparison without supports with FST15
 </t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>images/UP_01_v3_1 (without supports)_20261015_111735.png</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>{"LC1": 0.1484, "LC2": 0.2071, "LC3": 0.3885, "LC4": 0.2854, "LC5": 0.2487, "LC6": 0.2998, "LC7": 0.3459, "LC8": 0.0788, "LC9": 0.0788}</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2026-10-15 11:54:58</t>
         </is>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E30" t="n">
         <v>1149.1</v>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t xml:space="preserve">Smaller fillet on the upright
 </t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>images/UP_01_v3_2_20261015_115458.png</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>{"LC1": 0.1311, "LC2": 0.1734, "LC3": 0.3176, "LC4": 0.2332, "LC5": 0.2011, "LC6": 0.2437, "LC7": 0.2799, "LC8": 0.0669, "LC9": 0.0669}</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_2_LC1_20261015_115458.png", "LC2": "images/UP_01_v3_2_LC2_20261015_115458.png", "LC3": "images/UP_01_v3_2_LC3_20261015_115458.png", "LC4": "images/UP_01_v3_2_LC4_20261015_115458.png", "LC5": "images/UP_01_v3_2_LC5_20261015_115458.png", "LC6": "images/UP_01_v3_2_LC6_20261015_115458.png", "LC7": "images/UP_01_v3_2_LC7_20261015_115458.png", "LC8": "images/UP_01_v3_2_LC8_20261015_115746.png", "LC9": "images/UP_01_v3_2_LC9_20261015_115746.png"}</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2026-10-15 16:05:42</t>
         </is>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E31" t="n">
         <v>1145.42</v>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t xml:space="preserve">Make sure the clearences were obtained and had to reduce the fillets on the upright
 </t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>images/UP_01_v3_3_20261015_160541.png</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>{"LC1": 0.1443, "LC2": 0.1952, "LC3": 0.3579, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": 0.0738, "LC9": 0.0738}</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_3_LC1_20261015_160541.png", "LC2": "images/UP_01_v3_3_LC2_20261015_160541.png", "LC3": "images/UP_01_v3_3_LC3_20261015_160541.png", "LC8": "images/UP_01_v3_3_LC8_20261015_160541.png", "LC9": "images/UP_01_v3_3_LC9_20261015_160542.png"}</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2026-10-15 16:21:56</t>
         </is>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E32" t="n">
         <v>1146.28</v>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t xml:space="preserve">The 3.3 didint give the results i wanted so i changed a bit the low fillet to see if improves stiffness
 </t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>images/UP_01_v3_3_1_20261015_162156.png</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>{"LC1": 0.1443, "LC2": 0.1952, "LC3": 0.3579, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": 0.0738, "LC9": 0.0738}</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2026-10-15 16:26:11</t>
         </is>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E33" t="n">
         <v>1146.28</v>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t xml:space="preserve">The 3.3 didint give the results i wanted so i changed a bit the low fillet to see if improves stiffness
 </t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>images/UP_01_v3_3_1_20261015_162611.png</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>{"LC1": 0.1429, "LC2": 0.1936, "LC3": 0.3532, "LC4": 0.2577, "LC5": 0.2236, "LC6": 0.2743, "LC7": 0.3151, "LC8": 0.0728, "LC9": 0.0738}</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_3_1_LC1_20261015_162611.png", "LC2": "images/UP_01_v3_3_1_LC2_20261015_162611.png", "LC3": "images/UP_01_v3_3_1_LC3_20261015_162611.png", "LC8": "images/UP_01_v3_3_1_LC8_20261015_162611.png", "LC9": "images/UP_01_v3_3_1_LC9_20261015_162611.png"}</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E34" t="n">
         <v>114.52</v>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Upright Lid FST15</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
         <is>
           <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>2026-10-06 18:49:19</t>
         </is>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E35" t="n">
         <v>101.15</v>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Due to the less height is lighter</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
         <is>
           <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>FST15 (with all features)</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>2026-10-13 20:39:47</t>
         </is>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="E36" t="n">
         <v>120.04</v>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>2.0 (with all features)</t>
         </is>
       </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>2026-10-13 20:48:17</t>
         </is>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E37" t="n">
         <v>116.27</v>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Corrected dimensions and features</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>UP_03</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D52" s="1" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E38" t="n">
         <v>59.37</v>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Flor FST15</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To represent the FST15 part
+</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
         <is>
           <t>images\UP_03_vFST15_imagem.png</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Motor Pilot Spigot Register", "Nominal (mm)": "125", "Fit / Tolerance": "H7/h6 location fit", "Roughness / Notes": "Ra &lt;= 1.6 um (motor concentricity)"}, {"Interface / Feature": "Cooling Jacket O-Ring Groove", "Nominal (mm)": "2.5 depth x 3.5 width", "Fit / Tolerance": "+/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 0.8 um (prevents coolant leak)"}, {"Interface / Feature": "Motor Stator Torque Stoppage Keyways", "Nominal (mm)": "2x Keys", "Fit / Tolerance": "+/- 0.03 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (reacts motor stator torque)"}]</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Motor Front Plate providing machined sealing face for motor cooling jacket O-ring and reaction keys for motor stator torque against the upright. Retained as separate plate to guarantee seal integrity and quick motor swaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>UpperSupport Version</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-12 15:47:39</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">With all the features
-</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>images\UpperSupport Version_v1_0_imagem.png</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>UpperSupport Version</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-14 00:22:29</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>images/UpperSupport Version_v2_0_20261014_002229.png</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>UP_04</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:42:38</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Baseline motor back plate iteration for FST15 carry-over.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial O-Ring: 
+Axial O-Ring: </t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>images/UP_04_vFST15_20261017_114238.png</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "O-Ring Sealing Plane Flatness", "Nominal (mm)": "Sealing Face", "Fit / Tolerance": "Flat within 0.03 mm", "Roughness / Notes": "Ra &lt;= 0.8 um (cooling jacket face seal)"}, {"Interface / Feature": "Cable / Port Pass-Through Bore", "Nominal (mm)": "32", "Fit / Tolerance": "+0.2 / 0 mm", "Roughness / Notes": "Deburred, edge radius &gt;= 1.0 mm"}]</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Motor Back Plate providing an accessible visual installation plane for the motor cooling jacket O-ring, eliminating blind insertion leak risks during motor assembly, and shielding the upright cavity from thermal soak.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,8 +46,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,6 +128,27 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L39" headerRowCount="1">
+  <autoFilter ref="A1:L39"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Subassembly"/>
+    <tableColumn id="2" name="Part Name"/>
+    <tableColumn id="3" name="Version"/>
+    <tableColumn id="4" name="Date"/>
+    <tableColumn id="5" name="Weight (g)"/>
+    <tableColumn id="6" name="Description"/>
+    <tableColumn id="7" name="Specifications"/>
+    <tableColumn id="8" name="Image Path"/>
+    <tableColumn id="9" name="Stiffness Data"/>
+    <tableColumn id="10" name="LC Images"/>
+    <tableColumn id="11" name="Tolerancing Data"/>
+    <tableColumn id="12" name="Justification"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -415,6 +442,20 @@
   </sheetPr>
   <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -479,36 +520,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 14:09:09</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">This is a simplified transmission to make iteractions easier
 </t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Center Distance: 32mm
 Big Planet Diameter: 45.6mm
@@ -520,42 +561,42 @@
 Axles Diameter: 7mm</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>images\TD_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 14:50:41</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Center Distance: 32.5
 Big Planet Diameter: 49.1241
@@ -569,42 +610,42 @@
 sun gear diameter: 19.0199</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 14:52:08</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Its the rounded number of version v1.1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Center Distance: 32.5
 Big Planet Diameter: 49.5
@@ -618,42 +659,42 @@
 Sun Gear Diameter: 19.5</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>2026-10-12 11:01:13</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">New version to try </t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Center Distance: 30
 Big Planet Diameter: 46.5
@@ -667,298 +708,274 @@
 Sun Gear Diameter: 16</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>HB_01</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="1" t="n">
         <v>654.66</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>With equal features</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>images\HB_01_vFST15_imagem.png</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Inner Bearing Shaft Seat (d=80mm)", "Nominal (mm)": "80", "Fit / Tolerance": "k5 (+0.009 / +0.002 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground, mates with 61816 bearing)"}, {"Interface / Feature": "Seal Running Land / Counterface (d1=85mm)", "Nominal (mm)": "85", "Fit / Tolerance": "h11 (0 / -0.220 mm)", "Roughness / Notes": "Ra = 0.2 - 0.5 um (plunge ground, zero lead)"}, {"Interface / Feature": "Wheel Stud Pitch Circle (PCD)", "Nominal (mm)": "4x PCD 100", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Runout &lt; 0.02 mm (wheel rim pilot)"}, {"Interface / Feature": "Brake Rotor Mounting Face", "Nominal (mm)": "Flatness", "Fit / Tolerance": "Axial runout &lt; 0.015 mm", "Roughness / Notes": "Ra &lt;= 0.8 um (prevents brake shudder)"}]</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>HB_01</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 18:38:55</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="1" t="n">
         <v>609.24</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">68 mm of height compared to 77mm in FST15
 </t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>images\HB_01_v1_imagem.png</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Inner Bearing Shaft Seat (d=80mm)", "Nominal (mm)": "80", "Fit / Tolerance": "k5 (+0.009 / +0.002 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground, mates with 61816 bearing)"}, {"Interface / Feature": "Seal Running Land / Counterface (d1=85mm)", "Nominal (mm)": "85", "Fit / Tolerance": "h11 (0 / -0.220 mm)", "Roughness / Notes": "Ra = 0.2 - 0.5 um (plunge ground, zero lead)"}, {"Interface / Feature": "Wheel Stud Pitch Circle (PCD)", "Nominal (mm)": "4x PCD 100", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Runout &lt; 0.02 mm (wheel rim pilot)"}, {"Interface / Feature": "Brake Rotor Mounting Face", "Nominal (mm)": "Flatness", "Fit / Tolerance": "Axial runout &lt; 0.015 mm", "Roughness / Notes": "Ra &lt;= 0.8 um (prevents brake shudder)"}]</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>HB_01</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>2026-10-07 13:36:53</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="1" t="n">
         <v>596.3200000000001</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>the difference to 1.0 is due to missing the interface for the sleeve</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>images\HB_01_v1_1_imagem.png</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Inner Bearing Shaft Seat (d=80mm)", "Nominal (mm)": "80", "Fit / Tolerance": "k5 (+0.009 / +0.002 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground, mates with 61816 bearing)"}, {"Interface / Feature": "Seal Running Land / Counterface (d1=85mm)", "Nominal (mm)": "85", "Fit / Tolerance": "h11 (0 / -0.220 mm)", "Roughness / Notes": "Ra = 0.2 - 0.5 um (plunge ground, zero lead)"}, {"Interface / Feature": "Wheel Stud Pitch Circle (PCD)", "Nominal (mm)": "4x PCD 100", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Runout &lt; 0.02 mm (wheel rim pilot)"}, {"Interface / Feature": "Brake Rotor Mounting Face", "Nominal (mm)": "Flatness", "Fit / Tolerance": "Axial runout &lt; 0.015 mm", "Roughness / Notes": "Ra &lt;= 0.8 um (prevents brake shudder)"}]</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>HB_02</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:28:41</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Retaining Nut Thread / Bore", "Nominal (mm)": "M75x1.5", "Fit / Tolerance": "6H/6g", "Roughness / Notes": "Ra &lt;= 1.6 um (spindle axial retention)"}]</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>HB_07</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 18:44:16</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="1" t="n">
         <v>6.78</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2mm to ensure no contact between the bearing and the seal</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>images\HB_07_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Spacer Inner Bore", "Nominal (mm)": "80.5", "Fit / Tolerance": "+0.2 / 0 mm", "Roughness / Notes": "Ra &lt;= 3.2 um (clears 80mm spindle)"}, {"Interface / Feature": "Spacer Length (Face-to-Face)", "Nominal (mm)": "12.0", "Fit / Tolerance": "+/- 0.02 mm", "Roughness / Notes": "Parallelism &lt; 0.005 mm (sets bearing preload)"}]</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>61815</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="1" t="n">
         <v>149</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61815
 Datasheet: 61815</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 75 | Dynamic Load Cr (kN): 13.7 | Static Load C0r (kN): 13.4 | Speed Limit (rpm): 10000</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Shaft Seat (d=75mm)", "Nominal (mm)": "75", "Fit / Tolerance": "k5 (+0.009 / +0.002 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground)"}, {"Interface / Feature": "Housing Bore (D=95mm)", "Nominal (mm)": "95", "Fit / Tolerance": "H7 (+0.030 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um"}, {"Interface / Feature": "Shaft Shoulder (da min)", "Nominal (mm)": "78.2", "Fit / Tolerance": "da &gt;= 78.2 mm (h11)", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Housing Shoulder (Da max)", "Nominal (mm)": "91.8", "Fit / Tolerance": "Da &lt;= 91.8 mm (H11)", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Shaft Radial Runout", "Nominal (mm)": "75", "Fit / Tolerance": "IT4 (0.004 mm)", "Roughness / Notes": "Max permissible TIR"}]</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>61816</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Baseline motor back plate iteration for FST15 carry-over.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>d (Bore diameter): 80 mm
 D (Outside diameter): 100 mm
@@ -979,149 +996,159 @@
 f0 (Calculation factor): 16</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>images/61816_vOEM_20261017_103218.png</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Shaft Seat (d=80mm)", "Nominal (mm)": "80", "Fit / Tolerance": "k5 (+0.009 / +0.002 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground)"}, {"Interface / Feature": "Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um"}, {"Interface / Feature": "Shaft Shoulder (da min)", "Nominal (mm)": "83.2", "Fit / Tolerance": "da &gt;= 83.2 mm (h11)", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Housing Shoulder (Da max)", "Nominal (mm)": "96.8", "Fit / Tolerance": "Da &lt;= 96.8 mm (H11)", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Shaft Radial Runout", "Nominal (mm)": "80", "Fit / Tolerance": "IT4 (0.004 mm)", "Roughness / Notes": "Max permissible TIR"}, {"Interface / Feature": "Shoulder Axial Runout", "Nominal (mm)": "83.2", "Fit / Tolerance": "IT4 (0.005 mm)", "Roughness / Notes": "Perpendicularity to axis"}]</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>71815-TN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 71815-TN
 Datasheet: 71815</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 75 | Dynamic Load Cr (kN): 16.2 | Static Load C0r (kN): 18.1 | Speed Limit (rpm): 8500</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Shaft Seat (d=75mm)", "Nominal (mm)": "75", "Fit / Tolerance": "m5 (+0.015 / +0.006 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground)"}, {"Interface / Feature": "Housing Bore (D=95mm)", "Nominal (mm)": "95", "Fit / Tolerance": "J7 (+0.018 / -0.012 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (light preload)"}, {"Interface / Feature": "Shaft Shoulder (da min)", "Nominal (mm)": "79.5", "Fit / Tolerance": "da &gt;= 79.5 mm", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Housing Shoulder (Da max)", "Nominal (mm)": "90.5", "Fit / Tolerance": "Da &lt;= 90.5 mm", "Roughness / Notes": "ra max = 0.6 mm"}]</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>71816-TN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Schaeffler Bearing: 71816-TN
-Datasheet: 71816</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Inner D (mm): 80 | Dynamic Load Cr (kN): 16.5 | Static Load C0r (kN): 19.1 | Speed Limit (rpm): 8000</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Shaft Seat (d=80mm)", "Nominal (mm)": "80", "Fit / Tolerance": "m5 (+0.015 / +0.006 mm)", "Roughness / Notes": "Ra &lt;= 0.4 um (ground)"}, {"Interface / Feature": "Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "J7 (+0.018 / -0.012 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (light preload)"}, {"Interface / Feature": "Shaft Shoulder (da min)", "Nominal (mm)": "84.5", "Fit / Tolerance": "da &gt;= 84.5 mm", "Roughness / Notes": "ra max = 0.6 mm"}, {"Interface / Feature": "Housing Shoulder (Da max)", "Nominal (mm)": "95.5", "Fit / Tolerance": "Da &lt;= 95.5 mm", "Roughness / Notes": "ra max = 0.6 mm"}]</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schaeffler Bearing: 71816-TN
+Datasheet: https://medias.schaeffler.es/pt/produto/rotary/rolamentos%2c-mancais-de-deslizamento/rolamentos-de-esferas/rolamentos-de-esferas-de-contacto-angular/71816-tn/p/359213?redirect=true </t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>d (Bore diameter): 80 mm
+D (Outside diameter): 100 mm
+B (Width): 10 mm
+Cr (Basic dynamic load rating): 16.5 kN (16500 N)
+C0r (Basic static load rating): 19.1 kN (19100 N)
+Cur (Fatigue load limit): 1.24 kN (1240 N)
+nG (Limiting speed): 8000 rpm
+n_ref (Reference speed): 3900 rpm
+m (Bearing weight): 0.152 kg (152 g)
+da min (Min. shaft abutment diameter): 85.2 mm
+Da max (Max. housing abutment diameter): 96.8 mm
+Db max (Max. housing clearance diameter): 98 mm
+ra max (Max. shaft fillet radius): 0.6 mm
+ra1 max (Max. housing fillet radius): 0.3 mm
+rmin (Min. chamfer dimension): 0.6 mm
+r1 min (Min. chamfer dimension): 0.3 mm
+D1 (Outer ring shoulder diameter): 92 mm
+d1 (Inner ring shoulder diameter): 88 mm
+a (Load center distance): 42.8 mm
+alpha (Contact angle): 40 deg
+Tmin (Min. operating temp): -30 deg C
+Tmax (Max. operating temp): 120 deg C</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>images/71816-TN_vOEM_20261017_175026.png</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>85X100X9 HMSA10 V</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="1" t="n">
         <v>43.8</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 85X100X9 HMSA10 V
 Datasheet: https://www.skf.com/pt/products/industrial-seals/power-transmission-seals/radial-shaft-seals/general-industrial-applications/productid-85X100X9%20HMSA10%20V
-  85  ─────── Shaft diameter d1 = 85 mm (Upright sealing land)
-  100 ─────── Housing bore diameter D = 100 mm (Wheel hub internal seat)
-  9   ─────── Seal width b = 9 mm
-  HMS ─────── Rubber-covered outside diameter with corrugated/beaded OD profile
-  A   ─────── Integrated non-contacting auxiliary secondary dust lip
-  10  ─────── SKF Generation 10 hydrodynamic sealing lip with toroidal garter spring
-  V   ─────── Fluoroelastomer (FKM / Viton®) compound + Stainless Steel garter spring
 </t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>d1 (Shaft diameter): 85 mm
 D (Housing bore diameter): 100 mm
@@ -1137,1253 +1164,1505 @@
 Max Pressure Difference: 0.05 N/mm2</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>images/85X100X9 HMSA10 V_vOEM_20261017_104022.png</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Shaft Counterface (d1=85mm)", "Nominal (mm)": "85", "Fit / Tolerance": "h11 (0 / -0.220 mm)", "Roughness / Notes": "Ra = 0.2 - 0.5 um (plunge ground, zero lead)"}, {"Interface / Feature": "Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um"}, {"Interface / Feature": "Lead-in Chamfer", "Nominal (mm)": "15 to 30 deg", "Fit / Tolerance": "Length &gt;= 3 mm", "Roughness / Notes": "Edges rounded and burr-free"}, {"Interface / Feature": "Shaft Surface Hardness", "Nominal (mm)": "Contact zone", "Fit / Tolerance": "&gt;= 45 HRC (recommended 58 HRC)", "Roughness / Notes": "Case depth &gt;= 0.3 mm"}, {"Interface / Feature": "Dynamic Eccentricity / Runout", "Nominal (mm)": "7020 rpm", "Fit / Tolerance": "&lt; 0.05 mm", "Roughness / Notes": "Max permissible TIR"}]</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>### Radial Shaft Seal Analysis &amp; Selection (SKF HMSA10 V)
+In-wheel drivetrain design, the radial shaft seal forms the sealing barrier between the rotating wheel hub and the stationary upright.
+It fulfills two non-negotiable operational requirements:
+1. **Internal Fluid Retention:** Sealing the internal oil without leakage under dynamic track accelerations.
+2. **External Contaminant Exclusion:** Preventing dust, track derived particles and other liquids from contaminating the gearbox oil consequently damaging the internal components.
+This document provides a comparative engineering trade-off analysis explaining why the **SKF HMSA10 V** was selected over all alternative architectures (HMS5, RG/NBR, CRW1, CRWA1, Cassette seals, and PTFE seals).
+---
+#### 2. SKF Nomenclature
+The designated part is standardized according to **ISO 6194-1** and **DIN 3760**:
+$$\mathbf{85 \times 100 \times 9 \quad HMSA10 \quad V}$$
+| Code Element | Engineering Definition |
+| :---: | :--- |
+| **85** | Shaft Diameter ($d_1 = 85\text{ mm}$) |
+| **100** | Housing Bore Diameter ($D = 100\text{ mm}$) |
+| **9** | Seal Width ($b = 9\text{ mm}$) |
+| **HMS** | Rubber Outside Diameter |
+| **A** | Auxiliary Dust Lip |
+| **10** | SKF Generation 10 Geometry |
+| **V** | Fluoroelastomer (FKM / Viton®) |
+---
+#### 3. Comparative Decision
+1. **Outer Diameter Construction:**
+   * **Metal Cased (CRW1 / CRWA1): REJECTED.** Aluminum bore expands $88\ \mu\text{m}$ more than the steel case at $100^\circ\text{C}$, causing loss of press-fit so oil leakage.
+   * **Rubber Covered (HMS5 / HMSA10): PASSED.** Elastic beaded rubber maintains continuous static contact pressure across all thermal cycles.
+2. **External Contamination Exclusion:**
+   * **Single Lip (HMS5): REJECTED.** No dust lip, outside contaminants can enter.
+   * **Dual Lip (HMSA10): PASSED.** Secondary lip acts as a seal barrier against outside contaminants.
+3. **Elastomer Compound:**
+   * **Nitrile NBR (Suffix RG): REJECTED.** Dynamic contact temperature reaches $95\text{--}105^\circ\text{C}$ and RG seals are rated to a maximum of $100^\circ\text{C}$.
+   * **Fluoroelastomer FKM (Suffix V): SELECTED (SKF HMSA10 V).** Continuous $200^\circ\text{C}$ rating.
+---
+#### 4. Rationale
+##### 4.1 Rubber Outside Diameter (HMS) vs. Metal Outer Case (CRW1 / CRWA1)
+The wheel hub and upright are CNC-machined from aerospace-grade **Al 7075-T6**. Aluminum has an exceptionally high coefficient of thermal expansion compared to the low-carbon structural steel (DC04 / AISI 1008):
+* $\alpha_{\text{Al 7075-T6}} = 23.4 \times 10^{-6}\text{ K}^{-1}$ *(Source: ASM Handbook Vol. 2 &amp; MMPDS-01)*
+* $\alpha_{\text{Steel (DC04)}} = 11.7 \times 10^{-6}\text{ K}^{-1}$ *(Source: Shigley Table A-5 &amp; DIN EN 10130)*
+During track runs operating temperatures can reach $T_{\text{op}} \approx 100^\circ\text{C}$ ($\Delta T = 80\text{ K}$ above a $20^\circ\text{C}$ shop assembly).
+For the housing bore diameter $D = 100.0\text{ mm}$:
+$$\Delta D_{\text{Al}} = D \cdot \alpha_{\text{Al}} \cdot \Delta T = 100.0 \cdot (23.4 \times 10^{-6}) \cdot 80.0 = \mathbf{0.1872\text{ mm}} \quad (187.2\ \mu\text{m})$$
+$$\Delta D_{\text{Steel}} = D \cdot \alpha_{\text{Steel}} \cdot \Delta T = 100.0 \cdot (11.7 \times 10^{-6}) \cdot 80.0 = \mathbf{0.0936\text{ mm}} \quad (93.6\ \mu\text{m})$$
+$$\Delta \text{Clearance Expansion} = \Delta D_{\text{Al}} - \Delta D_{\text{Steel}} = 0.1872 - 0.0936 = \mathbf{0.0936\text{ mm}} \quad (\mathbf{93.6\ \mu\text{m}})$$
+**The Failure Mechanism of Metal-Cased Seals:** An unconstrained thermal expansion differential of $93.6\ \mu\text{m}$ is nearly double the standard interference press-fit interval (P7: max $-0.024\text{ mm}$; min $-0.059\text{ mm}$). Consequently, a metal-cased seal (like SKF CRW1 or CRWA1) completely loses retention, spins within the housing bore, and migrates axially, causing catastrophic oil leakage.
+**The HMS Advantage:** The vulcanized elastomer outer body features molded circumferential beads. The rubber retains elastic memory and continuous radial contact pressure against the aluminum bore across thermal cycles.
+---
+##### 4.2 Auxiliary Dust Lip (HMSA10) vs. Single Lip (HMS5)
+* **Single-Lip Seals (HMS5):** Possess only the primary, spring-loaded hydrodynamic sealing lip. While effective at fluid retention, they offer zero protection against external particulate matter.
+* **Dual-Lip Seals with Auxiliary Lip (HMSA10):** Integrate a secondary, non-spring-loaded elastomer lip facing the external environment.
+In Formula Student racing:
+1. Carbon-metallic brake pads generate microscopic abrasive dust immediately adjacent to the wheel seal.
+2. Hot Hoosier racing slicks shed molten rubber debris ("marbles") and track grit.
+3. If solid particles breach the sealing zone of an HMS5 seal, they embed under the lip, machining a severe circumferential wear groove into the shaft and tearing the flexible sealing edge.
+4. The auxiliary lip of the HMSA10 acts as a mechanical deflector. Because it operates with minimal interference, it excludes particulates without adding parasitic friction torque or excess underlip heat.
+---
+##### 4.3 Fluoroelastomer (V / FKM) vs. Nitrile Rubber (RG / NBR)
+| Performance Parameter | Nitrile Rubber (RG / NBR) | Fluoroelastomer (V / FKM) — Selected | Impact |
+| :--- | :---: | :---: | :--- |
+| **Continuous Temp Range** | $-40^\circ\text{C}$ to $+100^\circ\text{C}$ | $-20^\circ\text{C}$ to $+200^\circ\text{C}$ | Pushes contact zone temperatures to $95\text{--}105^\circ\text{C}$. |
+| **Peak Temperature Spike** | Up to $+120^\circ\text{C}$ | Up to $+250^\circ\text{C}$ | Provides immunity during post-braking heat soak in the paddock when airflow ceases. |
+| **Garter Spring Material** | Carbon Steel | Stainless Steel (AISI 302/304) | Eliminates spring corrosion |
+---
+#### 5. Operational Verification
+##### 5.1 Circumferential Surface Speed
+* Shaft diameter at seal: $d_1 = 85\text{ mm} = 0.085\text{ m}$
+* Peak wheel rotational speed: $n = 1650\text{ rpm}$
+$$v = \frac{\pi \cdot d_1 \cdot n}{60} = \frac{\pi \cdot 0.085 \cdot 1650}{60} = \mathbf{7.34\text{ m/s}}$$
+* **SKF HMSA10 V Limit:** $14\text{ m/s}$ continuous / $31.2\text{ m/s}$ max catalog rating.
+* **Safety Factor:** $\text{SF}_v = \frac{14}{7.34} \approx \mathbf{1.907}$
+---
+##### 5.2 Internal Pressure Differential
+###### 5.2.2 System Boundary
+With the baseline from FST15 Drivetrain Design Documentation (Section Oil Seal, pp. 33–34):
+* **Total Internal Cavity Volume ($V_{\text{total}}$):** The rigid internal envelope formed by the hub, upright, and lids is $V_{\text{total}} \approx 407.4\text{ ml}$.
+* **Initial Oil Charge ($V_{0,\text{oil}}$):** Liquid lubricant occupies $1/3$ of the internal volume:
+  $$V_{0,\text{oil}} = \frac{1}{3} V_{\text{total}} = \mathbf{135.80\text{ ml}}$$
+* **Initial Air Cushion ($V_{1,\text{air}}$):** The air occupying $2/3$ of the volume:
+  $$V_{1,\text{air}} = \frac{2}{3} V_{\text{total}} = \mathbf{271.60\text{ ml}}$$
+* **Thermal Boundary Conditions:**
+  * Initial assembly state: $T_1 = 15^\circ\text{C} = 15 + 273.15 = \mathbf{288.15\text{ K}}$, at atmospheric pressure $p_1 = p_{\text{atm}} = \mathbf{1.00\text{ bar}}$.
+  * Worst-case operating state: $T_2 = 100^\circ\text{C} = 100 + 273.15 = \mathbf{373.15\text{ K}}$.
+  * Effective thermal delta: $\Delta T = T_2 - T_1 = 100 - 15 = \mathbf{85\text{ K}}$.
+* **Oil Expansion Coefficient ($\beta$):** The volumetric thermal expansion coefficient for synthetic transmission gear oils is $\beta = 7.0 \times 10^{-4}\text{ K}^{-1}$.
+###### 5.2.3 Step-by-Step Mathematical Derivation
+1. **Volumetric Thermal Expansion of the Liquid Oil:**
+   The volume increase of the liquid lubricant under thermal excitation is given by:
+   $$\Delta V_{\text{oil}} = V_{0,\text{oil}} \cdot \beta \cdot \Delta T = 135.80\text{ ml} \times (7.0 \times 10^{-4}\text{ K}^{-1}) \times 85\text{ K} = \mathbf{8.08\text{ ml}}$$
+   The expanded oil volume at operating temperature becomes:
+   $$V_{2,\text{oil}} = V_{0,\text{oil}} + \Delta V_{\text{oil}} = 135.80\text{ ml} + 8.08\text{ ml} = \mathbf{143.88\text{ ml}}$$
+2. **Compression of the Trapped Air Headspace:**
+   Assuming a structurally rigid aluminum housing ($V_{\text{total}} = \text{constant}$), the expansion of the liquid oil directly reduces the available volume for the trapped air:
+   $$V_{2,\text{air}} = V_{1,\text{air}} - \Delta V_{\text{oil}}$$
+   $$V_{2,\text{air}} = 271.60\text{ ml} - 8.08\text{ ml} = \mathbf{263.52\text{ ml}}$$
+3. **Calculation of Final Internal Air Pressure (Combined Ideal Gas Law):**
+   $$p \cdot V = n \cdot R \cdot T$$
+   Because the wheel hub is hermetically enclosed by the radial shaft seal and stationary O-rings:
+   * **Zero Mass Transfer:** No air can escape the cavity, and no ambient air can enter ($m = \text{constant}$).
+   * **Constant State Product:** The product of the trapped air mass and the gas constant ($n \cdot R$) remains strictly constant throughout all thermal transitions.
+   Rearranging the state equation by dividing by $T$:
+   $$\frac{p_1 \cdot V_{1,\text{air}}}{T_1} = \frac{p_2 \cdot V_{2,\text{air}}}{T_2}$$
+   Solving explicitly for the final absolute internal pressure ($p_2$):
+   $$p_2 = p_1 \cdot \left(\frac{T_2}{T_1}\right) \cdot \left(\frac{V_{1,\text{air}}}{V_{2,\text{air}}}\right)$$
+   Substituting the numerical parameters:
+   $$p_2 = 1.00\text{ bar} \cdot \left(\frac{373.15\text{ K}}{288.15\text{ K}}\right) \cdot \left(\frac{271.60\text{ ml}}{263.52\text{ ml}}\right)$$
+   $$p_2 = 1.00 \cdot (1.2950) \cdot (1.0307) = \mathbf{1.3347\text{ bar}} \approx \mathbf{1.33\text{ bar}}$$
+4. **Net Differential Pressure Across the Sealing Lip ($\Delta p$):**
+   The relative pressure acting outward across the SKF HMSA10 V sealing lip is:
+   $$\Delta p = p_2 - p_{\text{atm}} = 1.3347\text{ bar} - 1.00\text{ bar} = \mathbf{0.3347\text{ bar}} \approx \mathbf{0.33\text{ bar}} \quad (0.033\text{ MPa})$$
+   Comparing the calculated operating differential pressure against the maximum catalog rating of the SKF HMSA10 V:
+   $$\Delta p = 0.33\text{ bar} &lt; \Delta p_{\text{max}} = 0.50\text{ bar} \implies \text{The HMSA10 V can withstand the thermal pressurization.}$$</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>95X110X9 HMSA10 V</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 95X110X9 HMSA10 V
 Datasheet: 95X110X9 </t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 95 | Outer D Min (mm): 110 | Width Min (mm): 9</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Shaft Counterface (d1=95mm)", "Nominal (mm)": "95", "Fit / Tolerance": "h11 (0 / -0.220 mm)", "Roughness / Notes": "Ra = 0.2 - 0.5 um (plunge ground, zero lead)"}, {"Interface / Feature": "Housing Bore (D=110mm)", "Nominal (mm)": "110", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um"}, {"Interface / Feature": "Lead-in Chamfer", "Nominal (mm)": "15 to 30 deg", "Fit / Tolerance": "Length &gt;= 3 mm", "Roughness / Notes": "Edges rounded and burr-free"}, {"Interface / Feature": "Dynamic Eccentricity / Runout", "Nominal (mm)": "7000 rpm", "Fit / Tolerance": "&lt; 0.05 mm", "Roughness / Notes": "Max permissible TIR"}]</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>### Radial Shaft Seal Analysis &amp; Selection (SKF HMSA10 V)
+In-wheel drivetrain design, the radial shaft seal forms the sealing barrier between the rotating wheel hub and the stationary upright.
+It fulfills two non-negotiable operational requirements:
+1. **Internal Fluid Retention:** Sealing the internal oil without leakage under dynamic track accelerations.
+2. **External Contaminant Exclusion:** Preventing dust, track derived particles and other liquids from contaminating the gearbox oil consequently damaging the internal components.
+This document provides a comparative engineering trade-off analysis explaining why the **SKF HMSA10 V** was selected over all alternative architectures (HMS5, RG/NBR, CRW1, CRWA1, Cassette seals, and PTFE seals).
+---
+#### 2. SKF Nomenclature
+The designated part is standardized according to **ISO 6194-1** and **DIN 3760**:
+$$\mathbf{85 \times 100 \times 9 \quad HMSA10 \quad V}$$
+| Code Element | Engineering Definition |
+| :---: | :--- |
+| **85** | Shaft Diameter ($d_1 = 85\text{ mm}$) |
+| **100** | Housing Bore Diameter ($D = 100\text{ mm}$) |
+| **9** | Seal Width ($b = 9\text{ mm}$) |
+| **HMS** | Rubber Outside Diameter |
+| **A** | Auxiliary Dust Lip |
+| **10** | SKF Generation 10 Geometry |
+| **V** | Fluoroelastomer (FKM / Viton®) |
+---
+#### 3. Comparative Decision
+1. **Outer Diameter Construction:**
+   * **Metal Cased (CRW1 / CRWA1): REJECTED.** Aluminum bore expands $88\ \mu\text{m}$ more than the steel case at $100^\circ\text{C}$, causing loss of press-fit so oil leakage.
+   * **Rubber Covered (HMS5 / HMSA10): PASSED.** Elastic beaded rubber maintains continuous static contact pressure across all thermal cycles.
+2. **External Contamination Exclusion:**
+   * **Single Lip (HMS5): REJECTED.** No dust lip, outside contaminants can enter.
+   * **Dual Lip (HMSA10): PASSED.** Secondary lip acts as a seal barrier against outside contaminants.
+3. **Elastomer Compound:**
+   * **Nitrile NBR (Suffix RG): REJECTED.** Dynamic contact temperature reaches $95\text{--}105^\circ\text{C}$ and RG seals are rated to a maximum of $100^\circ\text{C}$.
+   * **Fluoroelastomer FKM (Suffix V): SELECTED (SKF HMSA10 V).** Continuous $200^\circ\text{C}$ rating.
+---
+#### 4. Rationale
+##### 4.1 Rubber Outside Diameter (HMS) vs. Metal Outer Case (CRW1 / CRWA1)
+The wheel hub and upright are CNC-machined from aerospace-grade **Al 7075-T6**. Aluminum has an exceptionally high coefficient of thermal expansion compared to the low-carbon structural steel (DC04 / AISI 1008):
+* $\alpha_{\text{Al 7075-T6}} = 23.4 \times 10^{-6}\text{ K}^{-1}$ *(Source: ASM Handbook Vol. 2 &amp; MMPDS-01)*
+* $\alpha_{\text{Steel (DC04)}} = 11.7 \times 10^{-6}\text{ K}^{-1}$ *(Source: Shigley Table A-5 &amp; DIN EN 10130)*
+During track runs operating temperatures can reach $T_{\text{op}} \approx 100^\circ\text{C}$ ($\Delta T = 80\text{ K}$ above a $20^\circ\text{C}$ shop assembly).
+For the housing bore diameter $D = 100.0\text{ mm}$:
+$$\Delta D_{\text{Al}} = D \cdot \alpha_{\text{Al}} \cdot \Delta T = 100.0 \cdot (23.4 \times 10^{-6}) \cdot 80.0 = \mathbf{0.1872\text{ mm}} \quad (187.2\ \mu\text{m})$$
+$$\Delta D_{\text{Steel}} = D \cdot \alpha_{\text{Steel}} \cdot \Delta T = 100.0 \cdot (11.7 \times 10^{-6}) \cdot 80.0 = \mathbf{0.0936\text{ mm}} \quad (93.6\ \mu\text{m})$$
+$$\Delta \text{Clearance Expansion} = \Delta D_{\text{Al}} - \Delta D_{\text{Steel}} = 0.1872 - 0.0936 = \mathbf{0.0936\text{ mm}} \quad (\mathbf{93.6\ \mu\text{m}})$$
+**The Failure Mechanism of Metal-Cased Seals:** An unconstrained thermal expansion differential of $93.6\ \mu\text{m}$ is nearly double the standard interference press-fit interval (P7: max $-0.024\text{ mm}$; min $-0.059\text{ mm}$). Consequently, a metal-cased seal (like SKF CRW1 or CRWA1) completely loses retention, spins within the housing bore, and migrates axially, causing catastrophic oil leakage.
+**The HMS Advantage:** The vulcanized elastomer outer body features molded circumferential beads. The rubber retains elastic memory and continuous radial contact pressure against the aluminum bore across thermal cycles.
+---
+##### 4.2 Auxiliary Dust Lip (HMSA10) vs. Single Lip (HMS5)
+* **Single-Lip Seals (HMS5):** Possess only the primary, spring-loaded hydrodynamic sealing lip. While effective at fluid retention, they offer zero protection against external particulate matter.
+* **Dual-Lip Seals with Auxiliary Lip (HMSA10):** Integrate a secondary, non-spring-loaded elastomer lip facing the external environment.
+In Formula Student racing:
+1. Carbon-metallic brake pads generate microscopic abrasive dust immediately adjacent to the wheel seal.
+2. Hot Hoosier racing slicks shed molten rubber debris ("marbles") and track grit.
+3. If solid particles breach the sealing zone of an HMS5 seal, they embed under the lip, machining a severe circumferential wear groove into the shaft and tearing the flexible sealing edge.
+4. The auxiliary lip of the HMSA10 acts as a mechanical deflector. Because it operates with minimal interference, it excludes particulates without adding parasitic friction torque or excess underlip heat.
+---
+##### 4.3 Fluoroelastomer (V / FKM) vs. Nitrile Rubber (RG / NBR)
+| Performance Parameter | Nitrile Rubber (RG / NBR) | Fluoroelastomer (V / FKM) — Selected | Impact |
+| :--- | :---: | :---: | :--- |
+| **Continuous Temp Range** | $-40^\circ\text{C}$ to $+100^\circ\text{C}$ | $-20^\circ\text{C}$ to $+200^\circ\text{C}$ | Pushes contact zone temperatures to $95\text{--}105^\circ\text{C}$. |
+| **Peak Temperature Spike** | Up to $+120^\circ\text{C}$ | Up to $+250^\circ\text{C}$ | Provides immunity during post-braking heat soak in the paddock when airflow ceases. |
+| **Garter Spring Material** | Carbon Steel | Stainless Steel (AISI 302/304) | Eliminates spring corrosion |
+---
+#### 5. Operational Verification
+##### 5.1 Circumferential Surface Speed
+* Shaft diameter at seal: $d_1 = 85\text{ mm} = 0.085\text{ m}$
+* Peak wheel rotational speed: $n = 1650\text{ rpm}$
+$$v = \frac{\pi \cdot d_1 \cdot n}{60} = \frac{\pi \cdot 0.085 \cdot 1650}{60} = \mathbf{7.34\text{ m/s}}$$
+* **SKF HMSA10 V Limit:** $14\text{ m/s}$ continuous / $31.2\text{ m/s}$ max catalog rating.
+* **Safety Factor:** $\text{SF}_v = \frac{14}{7.34} \approx \mathbf{1.907}$
+---
+##### 5.2 Internal Pressure Differential
+###### 5.2.2 System Boundary
+With the baseline from FST15 Drivetrain Design Documentation (Section Oil Seal, pp. 33–34):
+* **Total Internal Cavity Volume ($V_{\text{total}}$):** The rigid internal envelope formed by the hub, upright, and lids is $V_{\text{total}} \approx 407.4\text{ ml}$.
+* **Initial Oil Charge ($V_{0,\text{oil}}$):** Liquid lubricant occupies $1/3$ of the internal volume:
+  $$V_{0,\text{oil}} = \frac{1}{3} V_{\text{total}} = \mathbf{135.80\text{ ml}}$$
+* **Initial Air Cushion ($V_{1,\text{air}}$):** The air occupying $2/3$ of the volume:
+  $$V_{1,\text{air}} = \frac{2}{3} V_{\text{total}} = \mathbf{271.60\text{ ml}}$$
+* **Thermal Boundary Conditions:**
+  * Initial assembly state: $T_1 = 15^\circ\text{C} = 15 + 273.15 = \mathbf{288.15\text{ K}}$, at atmospheric pressure $p_1 = p_{\text{atm}} = \mathbf{1.00\text{ bar}}$.
+  * Worst-case operating state: $T_2 = 100^\circ\text{C} = 100 + 273.15 = \mathbf{373.15\text{ K}}$.
+  * Effective thermal delta: $\Delta T = T_2 - T_1 = 100 - 15 = \mathbf{85\text{ K}}$.
+* **Oil Expansion Coefficient ($\beta$):** The volumetric thermal expansion coefficient for synthetic transmission gear oils is $\beta = 7.0 \times 10^{-4}\text{ K}^{-1}$.
+###### 5.2.3 Step-by-Step Mathematical Derivation
+1. **Volumetric Thermal Expansion of the Liquid Oil:**
+   The volume increase of the liquid lubricant under thermal excitation is given by:
+   $$\Delta V_{\text{oil}} = V_{0,\text{oil}} \cdot \beta \cdot \Delta T = 135.80\text{ ml} \times (7.0 \times 10^{-4}\text{ K}^{-1}) \times 85\text{ K} = \mathbf{8.08\text{ ml}}$$
+   The expanded oil volume at operating temperature becomes:
+   $$V_{2,\text{oil}} = V_{0,\text{oil}} + \Delta V_{\text{oil}} = 135.80\text{ ml} + 8.08\text{ ml} = \mathbf{143.88\text{ ml}}$$
+2. **Compression of the Trapped Air Headspace:**
+   Assuming a structurally rigid aluminum housing ($V_{\text{total}} = \text{constant}$), the expansion of the liquid oil directly reduces the available volume for the trapped air:
+   $$V_{2,\text{air}} = V_{1,\text{air}} - \Delta V_{\text{oil}}$$
+   $$V_{2,\text{air}} = 271.60\text{ ml} - 8.08\text{ ml} = \mathbf{263.52\text{ ml}}$$
+3. **Calculation of Final Internal Air Pressure (Combined Ideal Gas Law):**
+   $$p \cdot V = n \cdot R \cdot T$$
+   Because the wheel hub is hermetically enclosed by the radial shaft seal and stationary O-rings:
+   * **Zero Mass Transfer:** No air can escape the cavity, and no ambient air can enter ($m = \text{constant}$).
+   * **Constant State Product:** The product of the trapped air mass and the gas constant ($n \cdot R$) remains strictly constant throughout all thermal transitions.
+   Rearranging the state equation by dividing by $T$:
+   $$\frac{p_1 \cdot V_{1,\text{air}}}{T_1} = \frac{p_2 \cdot V_{2,\text{air}}}{T_2}$$
+   Solving explicitly for the final absolute internal pressure ($p_2$):
+   $$p_2 = p_1 \cdot \left(\frac{T_2}{T_1}\right) \cdot \left(\frac{V_{1,\text{air}}}{V_{2,\text{air}}}\right)$$
+   Substituting the numerical parameters:
+   $$p_2 = 1.00\text{ bar} \cdot \left(\frac{373.15\text{ K}}{288.15\text{ K}}\right) \cdot \left(\frac{271.60\text{ ml}}{263.52\text{ ml}}\right)$$
+   $$p_2 = 1.00 \cdot (1.2950) \cdot (1.0307) = \mathbf{1.3347\text{ bar}} \approx \mathbf{1.33\text{ bar}}$$
+4. **Net Differential Pressure Across the Sealing Lip ($\Delta p$):**
+   The relative pressure acting outward across the SKF HMSA10 V sealing lip is:
+   $$\Delta p = p_2 - p_{\text{atm}} = 1.3347\text{ bar} - 1.00\text{ bar} = \mathbf{0.3347\text{ bar}} \approx \mathbf{0.33\text{ bar}} \quad (0.033\text{ MPa})$$
+   Comparing the calculated operating differential pressure against the maximum catalog rating of the SKF HMSA10 V:
+   $$\Delta p = 0.33\text{ bar} &lt; \Delta p_{\text{max}} = 0.50\text{ bar} \implies \text{The HMSA10 V can withstand the thermal pressurization.}$$</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="1" t="n">
         <v>1049.81</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">To make a baseline </t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_vFST15_20261014_003807.png</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1758, "LC2": 0.2702, "LC3": 0.3631, "LC4": 0.285, "LC5": 0.2541, "LC6": 0.3201, "LC7": 0.3598, "LC8": 0.0835, "LC9": 0.0835}</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>2026-10-12 15:56:06</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="1" t="n">
         <v>973.05</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The new upper support design
 </t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Transmission: v1.2
 UpperSuport: v1.0</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.3429, "LC2": 0.3914, "LC3": 0.7797, "LC4": 0.5463, "LC5": 0.4658, "LC6": 0.6519, "LC7": 0.7425, "LC8": 0.1437, "LC9": 0.1437}</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>2026-10-12 16:58:21</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="1" t="n">
         <v>996.61</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Maked the side walls solid</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Transmission: v1.2
 UpperSuport: v1.0</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.2032, "LC2": 0.2119, "LC3": 0.4325, "LC4": 0.331, "LC5": 0.2905, "LC6": 0.3288, "LC7": 0.3826, "LC8": 0.0883, "LC9": 0.0883}</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>2.0 (without supports)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>2026-10-13 20:33:44</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="1" t="n">
         <v>532.01</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>For comparing weight before adding the suspension supports with the FST15 design</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v2_0 (without supports)_20261013_203344.png</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.0, "LC2": 0.0, "LC3": 0.0, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0, "LC9": 0.0}</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>FST15 (without supports)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>2026-10-13 20:35:55</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="1" t="n">
         <v>677.2</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>To make a baseline without the supports but with otimization of the transmission area</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Transmission: vFST15</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_vFST15 (without supports)_20261013_203555.png</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.0, "LC2": 0.0, "LC3": 0.0, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0, "LC9": 0.0}</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 00:25:37</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="1" t="n">
         <v>1029.86</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">To make a baseline </t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v2_0_20261014_002537.png</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.2451, "LC2": 0.231, "LC3": 0.4058, "LC4": 0.2989, "LC5": 0.2604, "LC6": 0.3203, "LC7": 0.367, "LC8": 0.0841, "LC9": 0.0841}</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>2.0.1</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 01:22:40</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="1" t="n">
         <v>1029.86</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">To make a baseline </t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1594, "LC2": 0.2208, "LC3": 0.4183, "LC4": 0.3058, "LC5": 0.2652, "LC6": 0.322, "LC7": 0.3708, "LC8": 0.0849, "LC9": 0.0849}</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 11:33:53</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="1" t="n">
         <v>1029.86</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>same supports as v2.0 but with bigger fillets in the pillars</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v2_1_20261014_113714.png</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1469, "LC2": 0.1923, "LC3": 0.3673, "LC4": 0.275, "LC5": 0.2377, "LC6": 0.2701, "LC7": 0.3129, "LC8": 0.0801, "LC9": 0.0801}</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 19:16:18</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="1" t="n">
         <v>1022.6</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>New try for the pillars and simpler uppersupports of v2.0</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_0_20261014_191617.png</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1597, "LC2": 0.2183, "LC3": 0.4255, "LC4": 0.3094, "LC5": 0.2667, "LC6": 0.3255, "LC7": 0.3747, "LC8": 0.0881, "LC9": 0.0881}</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_0_LC1_20261014_191617.png", "LC2": "images/UP_01_v3_0_LC2_20261014_191617.png", "LC3": "images/UP_01_v3_0_LC3_20261014_191617.png", "LC8": "images/UP_01_v3_0_LC8_20261014_191617.png", "LC4": "images/UP_01_v3_0_LC4_20261014_192056.png", "LC5": "images/UP_01_v3_0_LC5_20261014_192056.png", "LC6": "images/UP_01_v3_0_LC6_20261014_192056.png", "LC7": "images/UP_01_v3_0_LC7_20261014_192056.png"}</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 10:25:28</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="1" t="n">
         <v>1153.17</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Bigger fillets on the pillars</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_1_20261015_102528.png</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1248, "LC2": 0.1625, "LC3": 0.3052, "LC4": 0.2234, "LC5": 0.1917, "LC6": 0.2315, "LC7": 0.2664, "LC8": 0.0648, "LC9": 0.0648}</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_1_LC1_20261015_103709.png", "LC2": "images/UP_01_v3_1_LC2_20261015_103709.png", "LC3": "images/UP_01_v3_1_LC3_20261015_103709.png", "LC4": "images/UP_01_v3_1_LC4_20261015_103710.png", "LC5": "images/UP_01_v3_1_LC5_20261015_103710.png", "LC6": "images/UP_01_v3_1_LC6_20261015_103710.png", "LC7": "images/UP_01_v3_1_LC7_20261015_103710.png", "LC8": "images/UP_01_v3_1_LC8_20261015_103710.png", "LC9": "images/UP_01_v3_1_LC9_20261015_103710.png"}</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>FST15 (1 body)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 10:30:42</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="1" t="n">
         <v>1170.2</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>The baseline with one body. The fastest way to iterate</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Transmission: vFST15
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_vFST15 (1 body)_20261015_103042.png</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1664, "LC2": 0.2509, "LC3": 0.3437, "LC4": 0.2647, "LC5": 0.2364, "LC6": 0.2997, "LC7": 0.3382, "LC8": 0.076, "LC9": 0.076}</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_vFST15 (1 body)_LC1_20261015_103042.png", "LC2": "images/UP_01_vFST15 (1 body)_LC2_20261015_103042.png", "LC3": "images/UP_01_vFST15 (1 body)_LC3_20261015_103042.png", "LC4": "images/UP_01_vFST15 (1 body)_LC4_20261015_103042.png", "LC5": "images/UP_01_vFST15 (1 body)_LC5_20261015_103042.png", "LC6": "images/UP_01_vFST15 (1 body)_LC6_20261015_103042.png", "LC7": "images/UP_01_vFST15 (1 body)_LC7_20261015_103042.png", "LC8": "images/UP_01_vFST15 (1 body)_LC8_20261015_103042.png", "LC9": "images/UP_01_vFST15 (1 body)_LC9_20261015_103042.png"}</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>2.0 (1 body)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 10:51:55</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Sanity Check on the baseline
 </t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v2_0 (1 body)_20261015_105155.png</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1484, "LC2": 0.2071, "LC3": 0.3885, "LC4": 0.2854, "LC5": 0.2487, "LC6": 0.2998, "LC7": 0.3459, "LC8": 0.0788, "LC9": 0.0788}</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>3.1 (without supports)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 11:17:35</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="1" t="n">
         <v>693.88</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">For comparison without supports with FST15
 </t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_1 (without supports)_20261015_111735.png</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1484, "LC2": 0.2071, "LC3": 0.3885, "LC4": 0.2854, "LC5": 0.2487, "LC6": 0.2998, "LC7": 0.3459, "LC8": 0.0788, "LC9": 0.0788}</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 11:54:58</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="1" t="n">
         <v>1149.1</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Smaller fillet on the upright
 </t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_2_20261015_115458.png</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1311, "LC2": 0.1734, "LC3": 0.3176, "LC4": 0.2332, "LC5": 0.2011, "LC6": 0.2437, "LC7": 0.2799, "LC8": 0.0669, "LC9": 0.0669}</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_2_LC1_20261015_115458.png", "LC2": "images/UP_01_v3_2_LC2_20261015_115458.png", "LC3": "images/UP_01_v3_2_LC3_20261015_115458.png", "LC4": "images/UP_01_v3_2_LC4_20261015_115458.png", "LC5": "images/UP_01_v3_2_LC5_20261015_115458.png", "LC6": "images/UP_01_v3_2_LC6_20261015_115458.png", "LC7": "images/UP_01_v3_2_LC7_20261015_115458.png", "LC8": "images/UP_01_v3_2_LC8_20261015_115746.png", "LC9": "images/UP_01_v3_2_LC9_20261015_115746.png"}</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 16:05:42</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="1" t="n">
         <v>1145.42</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Make sure the clearences were obtained and had to reduce the fillets on the upright
 </t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_3_20261015_160541.png</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1443, "LC2": 0.1952, "LC3": 0.3579, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": 0.0738, "LC9": 0.0738}</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_3_LC1_20261015_160541.png", "LC2": "images/UP_01_v3_3_LC2_20261015_160541.png", "LC3": "images/UP_01_v3_3_LC3_20261015_160541.png", "LC8": "images/UP_01_v3_3_LC8_20261015_160541.png", "LC9": "images/UP_01_v3_3_LC9_20261015_160542.png"}</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 16:21:56</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="1" t="n">
         <v>1146.28</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The 3.3 didint give the results i wanted so i changed a bit the low fillet to see if improves stiffness
 </t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_3_1_20261015_162156.png</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1443, "LC2": 0.1952, "LC3": 0.3579, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": 0.0738, "LC9": 0.0738}</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 16:26:11</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="1" t="n">
         <v>1146.28</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The 3.3 didint give the results i wanted so i changed a bit the low fillet to see if improves stiffness
 </t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_3_1_20261015_162611.png</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1429, "LC2": 0.1936, "LC3": 0.3532, "LC4": 0.2577, "LC5": 0.2236, "LC6": 0.2743, "LC7": 0.3151, "LC8": 0.0728, "LC9": 0.0738}</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_3_1_LC1_20261015_162611.png", "LC2": "images/UP_01_v3_3_1_LC2_20261015_162611.png", "LC3": "images/UP_01_v3_3_1_LC3_20261015_162611.png", "LC8": "images/UP_01_v3_3_1_LC8_20261015_162611.png", "LC9": "images/UP_01_v3_3_1_LC9_20261015_162611.png"}</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Bearing Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H7 (+0.035 / 0 mm)", "Roughness / Notes": "Ra &lt;= 1.6 um (mates with 61816 bearing outer ring)"}, {"Interface / Feature": "Seal Housing Bore (D=100mm)", "Nominal (mm)": "100", "Fit / Tolerance": "H8 (+0.054 / 0 mm)", "Roughness / Notes": "Ra = 1.6 - 3.2 um (mates with 85x100x9 seal)"}, {"Interface / Feature": "Brake Caliper Mounting Bosses", "Nominal (mm)": "2x M8x1.25", "Fit / Tolerance": "Position +/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (radial caliper direct mount)"}, {"Interface / Feature": "Upper Wishbone Pickup Clevis", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (suspension spherical bearing pin)"}, {"Interface / Feature": "Steering Tie-Rod Pickup Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (steering link clevis)"}]</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="1" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="1" t="n">
         <v>114.52</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Upright Lid FST15</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 18:49:19</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="1" t="n">
         <v>101.15</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Due to the less height is lighter</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="1" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>FST15 (with all features)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="1" t="inlineStr">
         <is>
           <t>2026-10-13 20:39:47</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="1" t="n">
         <v>120.04</v>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>2.0 (with all features)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>2026-10-13 20:48:17</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="1" t="n">
         <v>116.27</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Corrected dimensions and features</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>UP_03</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="1" t="n">
         <v>59.37</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">To represent the FST15 part
 </t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>images\UP_03_vFST15_imagem.png</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Motor Pilot Spigot Register", "Nominal (mm)": "125", "Fit / Tolerance": "H7/h6 location fit", "Roughness / Notes": "Ra &lt;= 1.6 um (motor concentricity)"}, {"Interface / Feature": "Cooling Jacket O-Ring Groove", "Nominal (mm)": "2.5 depth x 3.5 width", "Fit / Tolerance": "+/- 0.05 mm", "Roughness / Notes": "Ra &lt;= 0.8 um (prevents coolant leak)"}, {"Interface / Feature": "Motor Stator Torque Stoppage Keyways", "Nominal (mm)": "2x Keys", "Fit / Tolerance": "+/- 0.03 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (reacts motor stator torque)"}]</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Motor Front Plate providing machined sealing face for motor cooling jacket O-ring and reaction keys for motor stator torque against the upright. Retained as separate plate to guarantee seal integrity and quick motor swaps.</t>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>### Front Plate Trade Study
+#### 1. Summary &amp; Context
+In previous Formula Student prototypes (e.g., FST14/FST15 with AMK DD5 motors), a dedicated **Motor Front Plate** was incorporated into the wheel assembly to fulfill two critical functions:
+1. **Cooling Jacket O-Ring Sealing:** Providing a machined sealing face and groove to isolate the motor cooling jacket from the transmission cavity.
+2. **Mechanical Stoppage:** Providing machined positive-locking slots/keys to react the motor stator torque reaction against the upright.
+For the **FST16** architecture, the powertrain transitions to the **DTI F-MOT** motor. This study demonstrates that both historical functions have been rendered completely obsolete by the motor's design.
+---
+#### 2. Functional Redundancy Analysis
+##### 2.1 Resolution of Sealing Interface (Function 1)
+The AMK motor lacked an integrated front sealing surface. The **DTI F-MOT** features an integrated front-face O-ring groove and sealing land. The motor seals directly against the upright mounting face, entirely eliminating the requirement for an intermediate plate.
+##### 2.2 Resolution of Stator Torque Reaction (Function 2)
+The legacy architecture relied on positive mechanical dogs/slots machined into the front plate to prevent motor casing rotation. To evaluate whether positive mechanical stops are required for the DTI motor, a fastener joint analysis was conducted under worst-case motor torque.
+---
+#### 3. Quantitative Structural &amp; Fastener Failure Mode Analysis
+The motor stator reacts against the upright through a circular pattern of **$6 \times \text{M}4$ bolts**.
+##### 3.1 Input Parameters
+| Parameter | Symbol | Value | Units | Description / Source |
+| :--- | :---: | :---: | :---: | :--- |
+| **Peak Motor Stator Torque** | $T_{\text{motor}}$ | **$31.6$** | $\text{N}\cdot\text{m}$ | Maximum peak torque capacity of DTI F-MOT |
+| **Bolt Circle Diameter** | $D_{\text{p}}$ | **$70.0$** | $\text{mm}$ | Bolt circle diameter ($r = 0.035\text{ m}$) |
+| **Fastener Specification** | — | **$6 \times \text{M}4$** | — | Grade 12.9 (Grade 10.9 baseline) |
+| **Fastener Tensile Stress Area** | $A_t$ | **$8.78$** | $\text{mm}^2$ | Standard ISO metric M4 thread area |
+| **Fastener Core (Minor) Area** | $A_{\text{core}}$ | **$7.24$** | $\text{mm}^2$ | Shear plane across minor thread diameter |
+| **Tightening Torque** | $T_{\text{tight}}$ | **$4.0$** | $\text{N}\cdot\text{m}$ | Assembly torque |
+| **Torque-Preload Coefficient** | $K$ | **$0.20$** | — | Standard zinc-plated / unlubricated coefficient |
+| **Friction Coefficient** | $\mu$ | **$0.15$** | — | Metal-on-metal interface (Al 7075-T6 to Steel) |
+| **Upright Flange Thickness** | $t_{\text{flange}}$ | **$5.0$** | $\text{mm}$ | Minimum flange thickness of upright |
+| **Upright Material** | — | **Al 7075-T6** | — | $S_y = 503\text{ MPa}$, $S_u = 572\text{ MPa}$ |
+---
+##### 3.2 Applied Tangential Shear Force
+The total tangential reaction force required to balance peak motor torque across the bolt circle radius ($r = 35\text{ mm}$):
+$$F_{\text{total, shear}} = \frac{T_{\text{motor}}}{r} = \frac{31.6\text{ N}\cdot\text{m}}{0.035\text{ m}} = \mathbf{902.86\text{ N}}$$
+Evenly distributed across the $n = 6$ fasteners:
+$$P_{\text{bolt}} = \frac{F_{\text{total, shear}}}{6} = \frac{902.86\text{ N}}{6} = \mathbf{150.48\text{ N per bolt}}$$
+---
+##### 3.3 Failure Mode 1: Joint Friction Slip (Primary Load Path)
+In a properly preloaded bolted assembly, tangential shear must be reacted entirely by **interface friction clamped by bolt pretension**, preventing any joint micro-slip or cyclical fastener bending.
+1. **Bolt Axial Preload ($F_i$):**
+   $$F_i = \frac{T_{\text{tight}}}{K \cdot d} = \frac{4.0\text{ N}\cdot\text{m}}{0.20 \times 0.004\text{ m}} = \mathbf{5000\text{ N}} \quad (5.0\text{ kN per bolt})$$
+2. **Bolt Tensile Stress &amp; Preload Safety Factor:**
+   $$\sigma_{\text{axial}} = \frac{F_i}{A_t} = \frac{5000\text{ N}}{8.78\text{ mm}^2} = \mathbf{569.48\text{ MPa}}$$
+   For Class 12.9 fasteners ($S_y = 1100\text{ MPa}$):
+   $$n_{\text{preload}} = \frac{S_y}{\sigma_{\text{axial}}} = \frac{1100\text{ MPa}}{569.48\text{ MPa}} = \mathbf{1.93} \quad (\text{Highly Safe})$$
+3. **Joint Frictional Clamping Torque Capacity ($T_{\text{friction}}$):**
+   $$T_{\text{friction}} = \mu \cdot \left(\sum F_i\right) \cdot r = \mu \cdot (n \cdot F_i) \cdot r$$
+   $$T_{\text{friction}} = 0.15 \cdot (6 \times 5000\text{ N}) \cdot 0.035\text{ m} = \mathbf{157.50\text{ N}\cdot\text{m}}$$
+4. **Safety Factor Against Joint Slip ($n_{\text{slip}}$):**
+   $$n_{\text{slip}} = \frac{T_{\text{friction}}}{T_{\text{motor}}} = \frac{157.50\text{ N}\cdot\text{m}}{31.6\text{ N}\cdot\text{m}} = \mathbf{4.98} \quad (\approx \mathbf{5.0})$$
+**Joint Slip Conclusion:** The clamping friction capacity ($157.5\text{ N}\cdot\text{m}$) is **5 times greater** than the maximum motor torque ($31.6\text{ N}\cdot\text{m}$). Under all racing conditions, the joint will remain 100% slip-free.
+---
+##### 3.4 Failure Mode 2: Bolt Direct Shear (Worst-Case Slipped Joint)
+Assuming complete loss of friction (e.g., severe grease contamination where $\mu \to 0$):
+1. **Direct Shear Stress across Minor Thread Diameter:**
+   $$\tau = \frac{P_{\text{bolt}}}{A_{\text{core}}} = \frac{150.48\text{ N}}{7.24\text{ mm}^2} = \mathbf{20.78\text{ MPa}}$$
+2. **Shear Yield Strength (Von Mises Distortion Energy Criterion):**
+   $$S_{sy} = 0.577 \cdot S_y$$
+   * For Class 12.9 ($S_y = 1100\text{ MPa}$): $S_{sy} = 0.577 \times 1100 = \mathbf{634.70\text{ MPa}}$
+   * For Class 10.9 ($S_y = 940\text{ MPa}$): $S_{sy} = 0.577 \times 940 = \mathbf{542.38\text{ MPa}}$
+3. **Safety Factor to Fastener Shear ($n_{\text{shear}}$):**
+   $$n_{\text{shear (12.9)}} = \frac{S_{sy}}{\tau} = \frac{634.70\text{ MPa}}{20.78\text{ MPa}} = \mathbf{30.5} \quad (\text{Immense Reserve})$$
+   $$n_{\text{shear (10.9)}} = \frac{542.38\text{ MPa}}{20.78\text{ MPa}} = \mathbf{26.1}$$
+---
+##### 3.5 Failure Mode 3: Upright Flange Hole Crushing / Bearing Stress
+If the joint slips and the bolt shanks bear directly against the hole walls in the Al 7075-T6 upright:
+1. **Projected Bearing Area:**
+   $$A_b = t_{\text{flange}} \cdot d_{\text{bolt}} = 5.0\text{ mm} \times 4.0\text{ mm} = \mathbf{20.00\text{ mm}^2}$$
+2. **Hole Wall Bearing Stress ($\sigma_{\text{bearing}}$):**
+   $$\sigma_{\text{bearing}} = \frac{P_{\text{bolt}}}{A_b} = \frac{150.48\text{ N}}{20.00\text{ mm}^2} = \mathbf{7.52\text{ MPa}}$$
+3. **Safety Factor Against Hole Wall Yielding ($n_{\text{bearing}}$):**
+   $$n_{\text{bearing}} = \frac{S_{y, \text{Al 7075-T6}}}{\sigma_{\text{bearing}}} = \frac{503.0\text{ MPa}}{7.52\text{ MPa}} = \mathbf{66.9} \quad (\text{Zero Risk of Elongation})$$
+---
+#### 4. Summary Matrix Across Bolt Property Classes
+| Sizing &amp; Failure Mode (In Sequence) | Class 12.9 (Optimal) | Class 10.9 (Standard) | Class 8.8 (Commercial) |
+| :--- | :---: | :---: | :---: |
+| **Applied Bolt Load (Slipped State)** | $150.5\text{ N}$ | $150.5\text{ N}$ | $150.5\text{ N}$ |
+| **1. Bolt Core Shear Stress ($\tau$)** | $20.8\text{ MPa}$ | $20.8\text{ MPa}$ | $20.8\text{ MPa}$ |
+| **Safety Factor: Bolt Shear ($n_{\text{shear}}$)** | **30.5** *(Immense)* | **26.1** *(Immense)* | **18.2** *(Highly Safe)* |
+| **2. Joint Frictional Torque Capacity** | $157.5\text{ N}\cdot\text{m}$ | $157.5\text{ N}\cdot\text{m}$ | $157.5\text{ N}\cdot\text{m}$ |
+| **Safety Factor: Joint Slip ($n_{\text{slip}}$)** | **4.98** *(Immense)* | **4.98** *(Immense)* | **4.98** *(Immense)* |
+| **Safety Factor: Preload Yield** | **1.93** *(Safe)* | **1.68** *(Safe)* | **1.16** *(Critical Risk)* |
+| **3. Upright Hole Bearing Stress** | $7.52\text{ MPa}$ | $7.52\text{ MPa}$ | $7.52\text{ MPa}$ |
+| **Safety Factor: Hole Wall Crushing** | **66.9** *(Immense)* | **66.9** *(Immense)* | **66.9** *(Immense)* |
+---
+#### 5. Conclusion
+**Decision: The Front Plate is declared completely obsolete and is permanently eliminated from the FST16 assembly.**
+* **Zero Functional Need:** The DTI motor provides native O-ring sealing, and the $6 \times \text{M}4$ bolt circle provides a **$5\times$ safety factor against friction slip** ($157.5\text{ N}\cdot\text{m}$ capacity vs. $31.6\text{ N}\cdot\text{m}$ demand), making anti-rotation slots redundant.
+* **Unsprung Mass Reduction:** Eliminates component mass and fastener overhead.
+* **Manufacturing &amp; Simplicity:** Removes an intermediate machined interface, eliminates stacked tolerances, and enables direct, rigid motor mounting to the upright structure.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>UP_04</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>2026-10-17 11:42:38</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="1" t="n">
         <v>40.02</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Baseline motor back plate iteration for FST15 carry-over.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Radial O-Ring: 
 Axial O-Ring: </t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>images/UP_04_vFST15_20261017_114238.png</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "O-Ring Sealing Plane Flatness", "Nominal (mm)": "Sealing Face", "Fit / Tolerance": "Flat within 0.03 mm", "Roughness / Notes": "Ra &lt;= 0.8 um (cooling jacket face seal)"}, {"Interface / Feature": "Cable / Port Pass-Through Bore", "Nominal (mm)": "32", "Fit / Tolerance": "+0.2 / 0 mm", "Roughness / Notes": "Deburred, edge radius &gt;= 1.0 mm"}]</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Motor Back Plate providing an accessible visual installation plane for the motor cooling jacket O-ring, eliminating blind insertion leak risks during motor assembly, and shielding the upright cavity from thermal soak.</t>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>### Backplate Rationale
+#### Component Trade-Off Study: Back Plate
+##### 1. Functional Definition
+The Motor Back Plate serves as an interface between the upright structure and the electric motor housing, fulfilling three primary engineering functions:
+* **Elimination of Blind O-Ring Assembly:** Provides an open, visually accessible installation plane for the motor cooling jacket O-ring, eliminating the risk of seal loss.
+* **Direct Inspection &amp; Rapid Maintenance:** Enables independent visual inspection and leak checks without requiring full motor extraction.
+* **Uniform Seal:** With the recommendation from DTI of using F6 for the internal upright geometry of the interface with the motor, this could lead to uneven force on the O-ring if the machined upright does come with a looser geometry.
+---
+##### 2. Marginal Mass Delta vs. System Risk
+Integrating the back plate into the main upright body yields a possible mass reduction of approximately $\approx 20\text{ g}$ against its $40\text{ g}$ baseline. This marginal $20\text{ g}$ saving is heavily outweighed by the heightened operational and manufacturing risks.
+---
+##### 3. Risk Mitigation
+The FST16 powertrain introduces significant major subsystem redesigns, including:
+* Transition to the DTI F-MOT motor architecture;
+* Integration of the new planetary gearset;
+* Complete redesign of drivetrain.
+Carrying over a proven, back plate design preserves known interface geometry, avoids development variables, and eliminates unnecessary design risk.
+---
+##### 4. Conclusion
+**Decision: The decoupled Back Plate component is retained for the FST16 wheel assembly.**
+The marginal mass saving ($\approx 20\text{ g}$) of one piece integration is unjustified when evaluated against the benefits in sealing reliability, manufacturing simplicity, trackside serviceability, reducing overall risk.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L39" headerRowCount="1">
-  <autoFilter ref="A1:L39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L41" headerRowCount="1">
+  <autoFilter ref="A1:L41"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Baseline motor back plate iteration for FST15 carry-over.</t>
+          <t>Schaeffler Deep Groove Ball Bearing 61816 (80x100x10 mm). Datasheet: 61816.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2302,35 +2302,48 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-21 18:41:40</t>
         </is>
       </c>
       <c r="E34" s="1" t="n">
-        <v>114.52</v>
+        <v>1125.14</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+          <t>Ulrima transmissãso</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v4.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
+          <t>images/UP_01_v4_1_20261021_184140.png</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": NaN, "LC2": NaN, "LC3": NaN, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": NaN, "LC9": NaN}</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
     </row>
@@ -2342,35 +2355,44 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-21 18:44:13</t>
         </is>
       </c>
       <c r="E35" s="1" t="n">
-        <v>101.15</v>
+        <v>1125.14</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>images\UP_02_v1_imagem.png</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
+          <t>Ulrima transmissãso</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v4.0
+Bodies: 1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": NaN, "LC2": NaN, "LC3": 0.3287, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": NaN, "LC9": NaN}</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
     </row>
@@ -2387,26 +2409,26 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E36" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+        <v>114.52</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Upright Lid FST15</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+          <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2427,30 +2449,26 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>2.0 (with all features)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:48:17</t>
+          <t>2026-10-06 18:49:19</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>116.27</v>
+        <v>101.15</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Corrected dimensions and features</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+          <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2466,38 +2484,122 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>FST15 (with all features)</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 20:39:47</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To represent the FST15 part
-</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
+        <v>120.04</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>2.0 (with all features)</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:48:17</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To represent the FST15 part
+</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>### Front Plate Trade Study
 #### 1. Summary &amp; Context
@@ -2590,50 +2692,50 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>UP_04</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>2026-10-17 11:42:38</t>
         </is>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E41" s="1" t="n">
         <v>40.02</v>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Baseline motor back plate iteration for FST15 carry-over.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Radial O-Ring: 
 Axial O-Ring: </t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>images/UP_04_vFST15_20261017_114238.png</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>### Backplate Rationale
 #### Component Trade-Off Study: Back Plate

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L41" headerRowCount="1">
-  <autoFilter ref="A1:L41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L39" headerRowCount="1">
+  <autoFilter ref="A1:L39"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>{"LC1": 0.1443, "LC2": 0.1952, "LC3": 0.3579, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": 0.0738, "LC9": 0.0738}</t>
+          <t>{"LC1": 0.1443, "LC2": 0.1952, "LC3": 0.3579, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0738, "LC9": 0.0738}</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15 16:21:56</t>
+          <t>2026-10-15 16:26:11</t>
         </is>
       </c>
       <c r="E32" s="1" t="n">
@@ -2224,17 +2224,17 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>images/UP_01_v3_3_1_20261015_162156.png</t>
+          <t>images/UP_01_v3_3_1_20261015_162611.png</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>{"LC1": 0.1443, "LC2": 0.1952, "LC3": 0.3579, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": 0.0738, "LC9": 0.0738}</t>
+          <t>{"LC1": 0.1429, "LC2": 0.1936, "LC3": 0.3532, "LC4": 0.2577, "LC5": 0.2236, "LC6": 0.2743, "LC7": 0.3151, "LC8": 0.0728, "LC9": 0.0738}</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"LC1": "images/UP_01_v3_3_1_LC1_20261015_162611.png", "LC2": "images/UP_01_v3_3_1_LC2_20261015_162611.png", "LC3": "images/UP_01_v3_3_1_LC3_20261015_162611.png", "LC8": "images/UP_01_v3_3_1_LC8_20261015_162611.png", "LC9": "images/UP_01_v3_3_1_LC9_20261015_162611.png"}</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
@@ -2253,42 +2253,41 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>3.3.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15 16:26:11</t>
+          <t>2026-10-21 18:44:13</t>
         </is>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1146.28</v>
+        <v>1126.36</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The 3.3 didint give the results i wanted so i changed a bit the low fillet to see if improves stiffness
-</t>
+          <t xml:space="preserve">Com a ultima transmissão e umas melhorias nos fillets </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Transmission: v2.0
+          <t>Transmission: v4.0
 Bodies: 1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>images/UP_01_v3_3_1_20261015_162611.png</t>
+          <t>images/UP_01_v4_1_20261021_235100.png</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>{"LC1": 0.1429, "LC2": 0.1936, "LC3": 0.3532, "LC4": 0.2577, "LC5": 0.2236, "LC6": 0.2743, "LC7": 0.3151, "LC8": 0.0728, "LC9": 0.0738}</t>
+          <t>{"LC1": 0.1298, "LC2": 0.1767, "LC3": 0.3163, "LC4": 0.2282, "LC5": 0.1969, "LC6": 0.2444, "LC7": 0.2797, "LC8": 0.0663, "LC9": 0.0663}</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>{"LC1": "images/UP_01_v3_3_1_LC1_20261015_162611.png", "LC2": "images/UP_01_v3_3_1_LC2_20261015_162611.png", "LC3": "images/UP_01_v3_3_1_LC3_20261015_162611.png", "LC8": "images/UP_01_v3_3_1_LC8_20261015_162611.png", "LC9": "images/UP_01_v3_3_1_LC9_20261015_162611.png"}</t>
+          <t>{"LC1": "images/UP_01_v4_1_LC1_20261021_234909.png", "LC2": "images/UP_01_v4_1_LC2_20261021_234909.png", "LC3": "images/UP_01_v4_1_LC3_20261021_234909.png", "LC8": "images/UP_01_v4_1_LC8_20261021_234909.png", "LC9": "images/UP_01_v4_1_LC9_20261021_234909.png", "LC4": "images/UP_01_v4_1_LC4_20261021_235418.png", "LC5": "images/UP_01_v4_1_LC5_20261021_235418.png", "LC6": "images/UP_01_v4_1_LC6_20261021_235418.png", "LC7": "images/UP_01_v4_1_LC7_20261021_235418.png"}</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
@@ -2302,48 +2301,35 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>UP_01</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>2026-10-21 18:41:40</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1125.14</v>
+        <v>114.52</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Ulrima transmissãso</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v4.0
-Bodies: 1</t>
-        </is>
-      </c>
+          <t>Upright Lid FST15</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>images/UP_01_v4_1_20261021_184140.png</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>{"LC1": NaN, "LC2": NaN, "LC3": NaN, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": NaN, "LC9": NaN}</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
+          <t>images\UP_02_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
     </row>
@@ -2355,44 +2341,35 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>UP_01</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>2026-10-21 18:44:13</t>
+          <t>2026-10-06 18:49:19</t>
         </is>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1125.14</v>
+        <v>101.15</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Ulrima transmissãso</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v4.0
-Bodies: 1</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>{"LC1": NaN, "LC2": NaN, "LC3": 0.3287, "LC4": NaN, "LC5": NaN, "LC6": NaN, "LC7": NaN, "LC8": NaN, "LC9": NaN}</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_02_v1_imagem.png</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
     </row>
@@ -2409,26 +2386,26 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>FST15 (with all features)</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 20:39:47</t>
         </is>
       </c>
       <c r="E36" s="1" t="n">
-        <v>114.52</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+        <v>120.04</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2449,26 +2426,30 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.0 (with all features)</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-13 20:48:17</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>101.15</v>
+        <v>116.27</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2484,122 +2465,38 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_03</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+        <v>59.37</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To represent the FST15 part
+</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+          <t>images\UP_03_vFST15_imagem.png</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>UP_02</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>2.0 (with all features)</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-13 20:48:17</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>116.27</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Corrected dimensions and features</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>UP_03</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>FST15</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:18:14</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To represent the FST15 part
-</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>### Front Plate Trade Study
 #### 1. Summary &amp; Context
@@ -2692,50 +2589,50 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>UP_04</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>2026-10-17 11:42:38</t>
         </is>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E39" s="1" t="n">
         <v>40.02</v>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Baseline motor back plate iteration for FST15 carry-over.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Radial O-Ring: 
 Axial O-Ring: </t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>images/UP_04_vFST15_20261017_114238.png</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>### Backplate Rationale
 #### Component Trade-Off Study: Back Plate

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L39" headerRowCount="1">
-  <autoFilter ref="A1:L39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L41" headerRowCount="1">
+  <autoFilter ref="A1:L41"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2301,35 +2301,48 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>4.1.1</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-23 10:08:37</t>
         </is>
       </c>
       <c r="E34" s="1" t="n">
-        <v>114.52</v>
+        <v>1120.57</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+          <t>Alterei a espessura da bridge entre pontos de fixação da tampa de 5mm da v4.1 para 3mm</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v4.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
+          <t>images/UP_01_v4_1_1_20261023_100837.png</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1305, "LC2": 0.1766, "LC3": 0.3191, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0672, "LC9": 0.0672}</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
     </row>
@@ -2341,35 +2354,49 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.1.2</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-23 10:18:00</t>
         </is>
       </c>
       <c r="E35" s="1" t="n">
-        <v>101.15</v>
+        <v>1120.57</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Alterei a espessura da bridge entre pontos de fixação da tampa de volta a 5mm e corrigi uma clearence
+</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v4.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
+          <t>images/UP_01_v4_1_1_20261023_100837.png</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1281, "LC2": 0.1725, "LC3": 0.3098, "LC4": 0.2238, "LC5": 0.1927, "LC6": 0.2389, "LC7": 0.2735, "LC8": 0.0653, "LC9": 0.0653}</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v4_1_2_LC1_20261023_103426.png", "LC2": "images/UP_01_v4_1_2_LC2_20261023_103426.png", "LC3": "images/UP_01_v4_1_2_LC3_20261023_103426.png", "LC8": "images/UP_01_v4_1_2_LC8_20261023_103426.png", "LC9": "images/UP_01_v4_1_2_LC9_20261023_103426.png", "LC4": "images/UP_01_v4_1_2_LC4_20261023_104100.png", "LC5": "images/UP_01_v4_1_2_LC5_20261023_104100.png", "LC6": "images/UP_01_v4_1_2_LC6_20261023_104100.png", "LC7": "images/UP_01_v4_1_2_LC7_20261023_104100.png"}</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
     </row>
@@ -2386,26 +2413,26 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E36" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+        <v>114.52</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Upright Lid FST15</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+          <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2426,30 +2453,26 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>2.0 (with all features)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:48:17</t>
+          <t>2026-10-06 18:49:19</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>116.27</v>
+        <v>101.15</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Corrected dimensions and features</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+          <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2465,38 +2488,122 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>FST15 (with all features)</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 20:39:47</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To represent the FST15 part
-</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
+        <v>120.04</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>2.0 (with all features)</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:48:17</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To represent the FST15 part
+</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>### Front Plate Trade Study
 #### 1. Summary &amp; Context
@@ -2589,50 +2696,50 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>UP_04</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>2026-10-17 11:42:38</t>
         </is>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E41" s="1" t="n">
         <v>40.02</v>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Baseline motor back plate iteration for FST15 carry-over.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Radial O-Ring: 
 Axial O-Ring: </t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>images/UP_04_vFST15_20261017_114238.png</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>### Backplate Rationale
 #### Component Trade-Off Study: Back Plate

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -2389,12 +2389,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>{"LC1": 0.1281, "LC2": 0.1725, "LC3": 0.3098, "LC4": 0.2238, "LC5": 0.1927, "LC6": 0.2389, "LC7": 0.2735, "LC8": 0.0653, "LC9": 0.0653}</t>
+          <t>{"LC1": 0.128, "LC2": 0.1725, "LC3": 0.3098, "LC4": 0.2238, "LC5": 0.1927, "LC6": 0.2389, "LC7": 0.2735, "LC8": 0.0653, "LC9": 0.0653}</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>{"LC1": "images/UP_01_v4_1_2_LC1_20261023_103426.png", "LC2": "images/UP_01_v4_1_2_LC2_20261023_103426.png", "LC3": "images/UP_01_v4_1_2_LC3_20261023_103426.png", "LC8": "images/UP_01_v4_1_2_LC8_20261023_103426.png", "LC9": "images/UP_01_v4_1_2_LC9_20261023_103426.png", "LC4": "images/UP_01_v4_1_2_LC4_20261023_104100.png", "LC5": "images/UP_01_v4_1_2_LC5_20261023_104100.png", "LC6": "images/UP_01_v4_1_2_LC6_20261023_104100.png", "LC7": "images/UP_01_v4_1_2_LC7_20261023_104100.png"}</t>
+          <t>{"LC1": "images/UP_01_v4_1_2_LC1_20261023_105914.png", "LC2": "images/UP_01_v4_1_2_LC2_20261023_105914.png", "LC3": "images/UP_01_v4_1_2_LC3_20261023_105914.png", "LC8": "images/UP_01_v4_1_2_LC8_20261023_103426.png", "LC9": "images/UP_01_v4_1_2_LC9_20261023_103426.png", "LC4": "images/UP_01_v4_1_2_LC4_20261023_104100.png", "LC5": "images/UP_01_v4_1_2_LC5_20261023_104100.png", "LC6": "images/UP_01_v4_1_2_LC6_20261023_104100.png", "LC7": "images/UP_01_v4_1_2_LC7_20261023_105820.png"}</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L41" headerRowCount="1">
-  <autoFilter ref="A1:L41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L42" headerRowCount="1">
+  <autoFilter ref="A1:L42"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2372,71 +2372,85 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">fiz rasgos na base dos eixos 
+</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v4.0
+Bodies: 1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_01_v4_1_2_20261023_114824.png</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.128, "LC2": 0.1725, "LC3": 0.3098, "LC4": 0.2238, "LC5": 0.1927, "LC6": 0.2389, "LC7": 0.2735, "LC8": 0.0653, "LC9": 0.0653}</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v4_1_2_LC1_20261023_105914.png", "LC2": "images/UP_01_v4_1_2_LC2_20261023_105914.png", "LC3": "images/UP_01_v4_1_2_LC3_20261023_105914.png", "LC8": "images/UP_01_v4_1_2_LC8_20261023_103426.png", "LC9": "images/UP_01_v4_1_2_LC9_20261023_103426.png", "LC4": "images/UP_01_v4_1_2_LC4_20261023_104100.png", "LC5": "images/UP_01_v4_1_2_LC5_20261023_104100.png", "LC6": "images/UP_01_v4_1_2_LC6_20261023_104100.png", "LC7": "images/UP_01_v4_1_2_LC7_20261023_105820.png"}</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>UP_01</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:45:50</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>1084.68</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Alterei a espessura da bridge entre pontos de fixação da tampa de volta a 5mm e corrigi uma clearence
 </t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Transmission: v4.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v4_1_1_20261023_100837.png</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>{"LC1": 0.128, "LC2": 0.1725, "LC3": 0.3098, "LC4": 0.2238, "LC5": 0.1927, "LC6": 0.2389, "LC7": 0.2735, "LC8": 0.0653, "LC9": 0.0653}</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>{"LC1": "images/UP_01_v4_1_2_LC1_20261023_105914.png", "LC2": "images/UP_01_v4_1_2_LC2_20261023_105914.png", "LC3": "images/UP_01_v4_1_2_LC3_20261023_105914.png", "LC8": "images/UP_01_v4_1_2_LC8_20261023_103426.png", "LC9": "images/UP_01_v4_1_2_LC9_20261023_103426.png", "LC4": "images/UP_01_v4_1_2_LC4_20261023_104100.png", "LC5": "images/UP_01_v4_1_2_LC5_20261023_104100.png", "LC6": "images/UP_01_v4_1_2_LC6_20261023_104100.png", "LC7": "images/UP_01_v4_1_2_LC7_20261023_105820.png"}</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>UP_02</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>FST15</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:18:14</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>114.52</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1291, "LC2": 0.1745, "LC3": 0.3177, "LC4": 0.2294, "LC5": 0.1974, "LC6": 0.2435, "LC7": 0.2791, "LC8": 0.0669, "LC9": 0.0669}</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v4_2_LC1_20261023_114550.png", "LC2": "images/UP_01_v4_2_LC2_20261023_114550.png", "LC3": "images/UP_01_v4_2_LC3_20261023_114550.png", "LC4": "images/UP_01_v4_2_LC4_20261023_114550.png", "LC5": "images/UP_01_v4_2_LC5_20261023_114550.png", "LC6": "images/UP_01_v4_2_LC6_20261023_114550.png", "LC7": "images/UP_01_v4_2_LC7_20261023_114550.png", "LC8": "images/UP_01_v4_2_LC8_20261023_114550.png", "LC9": "images/UP_01_v4_2_LC9_20261023_114550.png"}</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
     </row>
@@ -2453,26 +2467,26 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>101.15</v>
+        <v>114.52</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
+          <t>Upright Lid FST15</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
+          <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2493,26 +2507,26 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-06 18:49:19</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+        <v>101.15</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+          <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2533,22 +2547,18 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>2.0 (with all features)</t>
+          <t>FST15 (with all features)</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:48:17</t>
+          <t>2026-10-13 20:39:47</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>116.27</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Corrected dimensions and features</t>
-        </is>
-      </c>
+        <v>120.04</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
@@ -2556,7 +2566,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2572,38 +2582,82 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>2.0 (with all features)</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 20:48:17</t>
         </is>
       </c>
       <c r="E40" s="1" t="n">
-        <v>59.37</v>
+        <v>116.27</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">To represent the FST15 part
-</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To represent the FST15 part
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>### Front Plate Trade Study
 #### 1. Summary &amp; Context
@@ -2696,50 +2750,50 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>UP_04</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="D42" s="1" t="inlineStr">
         <is>
           <t>2026-10-17 11:42:38</t>
         </is>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E42" s="1" t="n">
         <v>40.02</v>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Baseline motor back plate iteration for FST15 carry-over.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Radial O-Ring: 
 Axial O-Ring: </t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>images/UP_04_vFST15_20261017_114238.png</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>### Backplate Rationale
 #### Component Trade-Off Study: Back Plate

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L42" headerRowCount="1">
-  <autoFilter ref="A1:L42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L44" headerRowCount="1">
+  <autoFilter ref="A1:L44"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2462,35 +2462,49 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>4.1.3</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-23 18:32:48</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>114.52</v>
+        <v>1136.03</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Alterei a espessura da bridge entre pontos de fixação da tampa para 8mm
+</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v4.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
+          <t>images/UP_01_v4_1_3_20261023_183248.png</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1269, "LC2": 0.1716, "LC3": 0.3024, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0637, "LC9": 0.0637}</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v4_1_3_LC1_20261023_183248.png", "LC2": "images/UP_01_v4_1_3_LC2_20261023_183248.png", "LC3": "images/UP_01_v4_1_3_LC3_20261023_183248.png", "LC8": "images/UP_01_v4_1_3_LC8_20261023_183248.png", "LC9": "images/UP_01_v4_1_3_LC9_20261023_183248.png"}</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
     </row>
@@ -2502,35 +2516,49 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-23 19:02:10</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>101.15</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Alterei a altura do pilar
+</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v4.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
+          <t>images/UP_01_v4_1_1_20261023_100837.png</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1323, "LC2": 0.1808, "LC3": 0.3019, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0632, "LC9": 0.0632}</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v4_3_LC1_20261023_190210.png", "LC2": "images/UP_01_v4_3_LC2_20261023_190210.png", "LC3": "images/UP_01_v4_3_LC3_20261023_190210.png", "LC8": "images/UP_01_v4_3_LC8_20261023_190210.png", "LC9": "images/UP_01_v4_3_LC9_20261023_190210.png"}</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
     </row>
@@ -2547,26 +2575,26 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+        <v>114.52</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Upright Lid FST15</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+          <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2587,30 +2615,26 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>2.0 (with all features)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:48:17</t>
+          <t>2026-10-06 18:49:19</t>
         </is>
       </c>
       <c r="E40" s="1" t="n">
-        <v>116.27</v>
+        <v>101.15</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Corrected dimensions and features</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+          <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2626,38 +2650,122 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>FST15 (with all features)</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 20:39:47</t>
         </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To represent the FST15 part
-</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
+        <v>120.04</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>2.0 (with all features)</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:48:17</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To represent the FST15 part
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>### Front Plate Trade Study
 #### 1. Summary &amp; Context
@@ -2750,50 +2858,50 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>UP_04</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>2026-10-17 11:42:38</t>
         </is>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E44" s="1" t="n">
         <v>40.02</v>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Baseline motor back plate iteration for FST15 carry-over.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Radial O-Ring: 
 Axial O-Ring: </t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>images/UP_04_vFST15_20261017_114238.png</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>### Backplate Rationale
 #### Component Trade-Off Study: Back Plate

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L44" headerRowCount="1">
-  <autoFilter ref="A1:L44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L46" headerRowCount="1">
+  <autoFilter ref="A1:L46"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2530,11 +2530,11 @@
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0</v>
+        <v>1129.22</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alterei a altura do pilar
+          <t xml:space="preserve">Alterei a altura do pilar, e aumentei o fillet da tampa do portacubo com a tampa
 </t>
         </is>
       </c>
@@ -2546,17 +2546,17 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>images/UP_01_v4_1_1_20261023_100837.png</t>
+          <t>images/UP_01_v4_3_20261024_092135.png</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>{"LC1": 0.1323, "LC2": 0.1808, "LC3": 0.3019, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0632, "LC9": 0.0632}</t>
+          <t>{"LC1": 0.1323, "LC2": 0.1808, "LC3": 0.3019, "LC4": 0.22, "LC5": 0.1914, "LC6": 0.2409, "LC7": 0.274, "LC8": 0.0632, "LC9": 0.0632}</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>{"LC1": "images/UP_01_v4_3_LC1_20261023_190210.png", "LC2": "images/UP_01_v4_3_LC2_20261023_190210.png", "LC3": "images/UP_01_v4_3_LC3_20261023_190210.png", "LC8": "images/UP_01_v4_3_LC8_20261023_190210.png", "LC9": "images/UP_01_v4_3_LC9_20261023_190210.png"}</t>
+          <t>{"LC1": "images/UP_01_v4_3_LC1_20261023_190210.png", "LC2": "images/UP_01_v4_3_LC2_20261023_190210.png", "LC3": "images/UP_01_v4_3_LC3_20261023_190210.png", "LC8": "images/UP_01_v4_3_LC8_20261023_190210.png", "LC9": "images/UP_01_v4_3_LC9_20261023_190210.png", "LC4": "images/UP_01_v4_3_LC4_20261024_091654.png", "LC5": "images/UP_01_v4_3_LC5_20261024_091654.png", "LC6": "images/UP_01_v4_3_LC6_20261024_091654.png", "LC7": "images/UP_01_v4_3_LC7_20261024_091654.png"}</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
@@ -2570,35 +2570,49 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-24 10:53:43</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>114.52</v>
+        <v>1090.66</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">USando os pilares ate ao planeta grande (v4.3) criei slots maquinaveis na interface com o motor
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v5.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
+          <t>images/UP_01_v4_3_1_20261024_105343.png</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1332, "LC2": 0.1834, "LC3": 0.3074, "LC4": 0.2229, "LC5": 0.1938, "LC6": 0.2452, "LC7": 0.2789, "LC8": 0.0641, "LC9": 0.0641}</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v4_3_1_LC1_20261024_105343.png", "LC2": "images/UP_01_v4_3_1_LC2_20261024_105343.png", "LC3": "images/UP_01_v4_3_1_LC3_20261024_105343.png", "LC4": "images/UP_01_v4_3_1_LC4_20261024_105343.png", "LC5": "images/UP_01_v4_3_1_LC5_20261024_105343.png", "LC6": "images/UP_01_v4_3_1_LC6_20261024_105343.png", "LC7": "images/UP_01_v4_3_1_LC7_20261024_105343.png", "LC8": "images/UP_01_v4_3_1_LC8_20261024_105343.png", "LC9": "images/UP_01_v4_3_1_LC9_20261024_105343.png"}</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
     </row>
@@ -2610,35 +2624,49 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-24 12:29:29</t>
         </is>
       </c>
       <c r="E40" s="1" t="n">
-        <v>101.15</v>
+        <v>1098.53</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Melhorei a geometria dos pilares no portacubo e melhorei os slots da interface do motor
+</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v5.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t>images/UP_01_v4_3_2_20261024_122929.png</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1304, "LC2": 0.1767, "LC3": 0.2964, "LC4": 0.2159, "LC5": 0.1876, "LC6": 0.2356, "LC7": 0.2682, "LC8": 0.0623, "LC9": 0.0623}</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v4_3_2_LC1_20261024_123906.png", "LC2": "images/UP_01_v4_3_2_LC2_20261024_123907.png", "LC3": "images/UP_01_v4_3_2_LC3_20261024_123907.png", "LC8": "images/UP_01_v4_3_2_LC8_20261024_123907.png", "LC9": "images/UP_01_v4_3_2_LC9_20261024_123907.png", "LC4": "images/UP_01_v4_3_2_LC4_20261024_124535.png", "LC5": "images/UP_01_v4_3_2_LC5_20261024_124535.png", "LC6": "images/UP_01_v4_3_2_LC6_20261024_124535.png", "LC7": "images/UP_01_v4_3_2_LC7_20261024_124535.png"}</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
     </row>
@@ -2655,26 +2683,26 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+        <v>114.52</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Upright Lid FST15</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+          <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2695,30 +2723,26 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>2.0 (with all features)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:48:17</t>
+          <t>2026-10-06 18:49:19</t>
         </is>
       </c>
       <c r="E42" s="1" t="n">
-        <v>116.27</v>
+        <v>101.15</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Corrected dimensions and features</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+          <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2734,38 +2758,122 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>FST15 (with all features)</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 20:39:47</t>
         </is>
       </c>
       <c r="E43" s="1" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To represent the FST15 part
-</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
+        <v>120.04</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>UP_02</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>2.0 (with all features)</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:48:17</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To represent the FST15 part
+</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>### Front Plate Trade Study
 #### 1. Summary &amp; Context
@@ -2858,50 +2966,50 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>UP_04</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t>2026-10-17 11:42:38</t>
         </is>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E46" s="1" t="n">
         <v>40.02</v>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Baseline motor back plate iteration for FST15 carry-over.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Radial O-Ring: 
 Axial O-Ring: </t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>images/UP_04_vFST15_20261017_114238.png</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>### Backplate Rationale
 #### Component Trade-Off Study: Back Plate

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L46" headerRowCount="1">
-  <autoFilter ref="A1:L46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L47" headerRowCount="1">
+  <autoFilter ref="A1:L47"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -808,30 +808,39 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>2026-10-07 13:36:53</t>
+          <t>2026-10-24 19:37:08</t>
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>596.3200000000001</v>
+        <v>618.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>the difference to 1.0 is due to missing the interface for the sleeve</t>
+          <t xml:space="preserve">The first iteration of the FST16 hub
+</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>images\HB_01_v1_1_imagem.png</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+          <t>images/HB_01_v5_0_20261024_193708.png</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.03341, "LC2": 0.02446, "LC3": 0.22401, "LC4": 0.16215, "LC5": 0.13324, "LC6": 0.11568, "LC7": 0.15095}</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/HB_01_v5_0_LC1_20261024_193900.png", "LC2": "images/HB_01_v5_0_LC2_20261024_193900.png", "LC3": "images/HB_01_v5_0_LC3_20261024_193900.png", "LC4": "images/HB_01_v5_0_LC4_20261024_193900.png", "LC5": "images/HB_01_v5_0_LC5_20261024_193900.png", "LC6": "images/HB_01_v5_0_LC6_20261024_193900.png", "LC7": "images/HB_01_v5_0_LC7_20261024_193900.png"}</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
     </row>
@@ -2678,35 +2687,49 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>UP_02</t>
+          <t>UP_01</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-24 17:30:49</t>
         </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>114.52</v>
+        <v>1060.69</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Upright Lid FST15</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Corte no LowerSupport e aumento da largura do tierod
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v5.0
+Bodies: 1</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
+          <t>images/UP_01_v6_0_20261024_173049.png</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1536, "LC2": 0.179, "LC3": 0.2967, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0648, "LC9": 0.0648}</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_01_v6_0_LC1_20261024_173049.png", "LC2": "images/UP_01_v6_0_LC2_20261024_173049.png", "LC3": "images/UP_01_v6_0_LC3_20261024_173049.png", "LC8": "images/UP_01_v6_0_LC8_20261024_173049.png", "LC9": "images/UP_01_v6_0_LC9_20261024_173049.png"}</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
     </row>
@@ -2723,26 +2746,26 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>FST15</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:49:19</t>
+          <t>2026-10-06 11:18:14</t>
         </is>
       </c>
       <c r="E42" s="1" t="n">
-        <v>101.15</v>
+        <v>114.52</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Due to the less height is lighter</t>
+          <t>Upright Lid FST15</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>images\UP_02_v1_imagem.png</t>
+          <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2763,26 +2786,26 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>FST15 (with all features)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:39:47</t>
+          <t>2026-10-06 18:49:19</t>
         </is>
       </c>
       <c r="E43" s="1" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Transmission: v2.0</t>
-        </is>
-      </c>
+        <v>101.15</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Due to the less height is lighter</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
+          <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2803,22 +2826,18 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>2.0 (with all features)</t>
+          <t>FST15 (with all features)</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:48:17</t>
+          <t>2026-10-13 20:39:47</t>
         </is>
       </c>
       <c r="E44" s="1" t="n">
-        <v>116.27</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Corrected dimensions and features</t>
-        </is>
-      </c>
+        <v>120.04</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
@@ -2826,7 +2845,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
+          <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2842,38 +2861,82 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>UP_03</t>
+          <t>UP_02</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>2.0 (with all features)</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:14</t>
+          <t>2026-10-13 20:48:17</t>
         </is>
       </c>
       <c r="E45" s="1" t="n">
-        <v>59.37</v>
+        <v>116.27</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">To represent the FST15 part
-</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
+          <t>Corrected dimensions and features</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>images\UP_03_vFST15_imagem.png</t>
+          <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>UP_03</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:14</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To represent the FST15 part
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>images\UP_03_vFST15_imagem.png</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>### Front Plate Trade Study
 #### 1. Summary &amp; Context
@@ -2966,50 +3029,50 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>UP_04</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D47" s="1" t="inlineStr">
         <is>
           <t>2026-10-17 11:42:38</t>
         </is>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E47" s="1" t="n">
         <v>40.02</v>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Baseline motor back plate iteration for FST15 carry-over.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Radial O-Ring: 
 Axial O-Ring: </t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>images/UP_04_vFST15_20261017_114238.png</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>### Backplate Rationale
 #### Component Trade-Off Study: Back Plate

--- a/FST16_DT_Parts_Export.xlsx
+++ b/FST16_DT_Parts_Export.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L47" headerRowCount="1">
-  <autoFilter ref="A1:L47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsTable" displayName="PartsTable" ref="A1:L63" headerRowCount="1">
+  <autoFilter ref="A1:L63"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -740,17 +740,25 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>With equal features</t>
+          <t>nTop Analysis on FST15 model to create a baseline</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>images\HB_01_vFST15_imagem.png</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>images/HB_01_FST15_20261025092325_1.png</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.02295,"LC2":0.01838,"LC3":0.15131,"LC4":0.11793,"LC5":0.09681,"LC6":0.08385,"LC7":0.10998,"LC8":0.0372,"LC9":0.0372}</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/HB_01_vFST15_LC1_20261006111814.png", "LC2": "images/HB_01_vFST15_LC2_20261006111814.png", "LC3": "images/HB_01_vFST15_LC3_20261006111814.png", "LC4": "images/HB_01_vFST15_LC4_20261006111814.png", "LC6": "images/HB_01_vFST15_LC6_20261006111814.png", "LC7": "images/HB_01_vFST15_LC7_20261006111814.png"}</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
     </row>
@@ -852,25 +860,43 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>HB_02</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>1</v>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>5.0.1</t>
+        </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 11:28:41</t>
+          <t>2026-10-25 09:45:04</t>
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
+        <v>709</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>The star body was filled with material</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>["images/HB_01_v5_0_1_20261025095029_1.png","images/HB_01_v5_0_1_20261025095049_1.png"]</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.02506,"LC2":0.0176,"LC3":0.15281,"LC4":0.11196,"LC5":0.09239,"LC6":0.07893,"LC7":0.10304}</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/HB_01_v5_0_1_LC1_20261025094504.png", "LC2": "images/HB_01_v5_0_1_LC2_20261025094504.png", "LC3": "images/HB_01_v5_0_1_LC3_20261025094504.png", "LC4": "images/HB_01_v5_0_1_LC4_20261025094504.png", "LC5": "images/HB_01_v5_0_LC5_20261024_193900.png", "LC6": "images/HB_01_v5_0_1_LC6_20261025094504.png", "LC7": "images/HB_01_v5_0_1_LC7_20261025094504.png"}</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
     </row>
@@ -882,109 +908,761 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>HB_07</t>
+          <t>HB_01</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0.2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06 18:44:16</t>
+          <t>2026-10-25 10:55:51</t>
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>6.78</v>
+        <v>585.65</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2mm to ensure no contact between the bearing and the seal</t>
+          <t>the ribs were maked bigger and the star body smaller</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>images\HB_07_v1_0_imagem.png</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+          <t>["images/HB_01_v5_0_1_20261025095029_1.png","images/HB_01_v5_0_1_20261025095049_1.png"]</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.02834,"LC2":0.02354,"LC3":0.17199,"LC4":0.1251,"LC5":0.1027,"LC6":0.08934,"LC7":0.117}</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/HB_01_v5_0_2_LC1_20261025105551.png", "LC2": "images/HB_01_v5_0_2_LC2_20261025105551.png", "LC3": "images/HB_01_v5_0_2_LC3_20261025105551.png", "LC4": "images/HB_01_v5_0_2_LC4_20261025105551.png", "LC5": "images/HB_01_v5_0_LC5_20261024_193900.png", "LC6": "images/HB_01_v5_0_2_LC6_20261025105551.png", "LC7": "images/HB_01_v5_0_2_LC7_20261025105551.png"}</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>5.0.3</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:51:28</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>570</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>the ribs were maked bigger and the star body smaller</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>["images/HB_01_v5_0_1_20261025095029_1.png","images/HB_01_v5_0_1_20261025095049_1.png"]</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.02733,"LC2":0.02221,"LC3":0.14391,"LC4":0.10467,"LC5":0.08601,"LC6":0.07515,"LC7":0.09844,"LC8":0.02641,"LC9":0.02641}</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/HB_01_v5_0_3_LC1_20261025125128.png", "LC2": "images/HB_01_v5_0_3_LC2_20261025125128.png", "LC3": "images/HB_01_v5_0_3_LC3_20261025125128.png", "LC4": "images/HB_01_v5_0_3_LC4_20261025125128.png", "LC5": "images/HB_01_v5_0_3_LC5_20261025125128.png", "LC6": "images/HB_01_v5_0_3_LC6_20261025125128.png", "LC7": "images/HB_01_v5_0_3_LC7_20261025125128.png"}</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>5.0.4</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-25 15:45:18</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>588.86</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>the ribs were maked bigger and the star body smaller</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>["images/HB_01_v5_0_1_20261025095029_1.png","images/HB_01_v5_0_1_20261025095049_1.png"]</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.02498,"LC2":0.01853,"LC3":0.14131,"LC4":0.10351,"LC5":0.08539,"LC6":0.07374,"LC7":0.09649,"LC8":0.0318,"LC9":0.0318}</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/HB_01_v5_0_4_LC1_20261025154518.png", "LC2": "images/HB_01_v5_0_4_LC2_20261025154518.png", "LC3": "images/HB_01_v5_0_4_LC3_20261025154518.png", "LC4": "images/HB_01_v5_0_4_LC4_20261025154518.png", "LC5": "images/HB_01_v5_0_4_LC5_20261025154518.png", "LC6": "images/HB_01_v5_0_4_LC6_20261025154518.png", "LC7": "images/HB_01_v5_0_4_LC7_20261025154518.png"}</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>5.0.5</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-26 11:26:00</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>576.73</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>The Fins were reduced to 16º and some general mimprovements of the ribs</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>images/HB_01_v5_0_5_20261026112600_sch.png</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.0276,"LC2":0.02263,"LC3":0.14329,"LC4":0.10532,"LC5":0.08693,"LC6":0.07522,"LC7":0.09828,"LC8":0.0308,"LC9":0.0308}</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/HB_01_v5_0_5_LC1_20261026112600.png", "LC2": "images/HB_01_v5_0_5_LC2_20261026112600.png", "LC3": "images/HB_01_v5_0_5_LC3_20261026112600.png", "LC4": "images/HB_01_v5_0_5_LC4_20261026112600.png", "LC5": "images/HB_01_v5_0_5_LC5_20261026112600.png", "LC6": "images/HB_01_v5_0_5_LC6_20261026112600.png", "LC7": "images/HB_01_v5_0_5_LC7_20261026112600.png"}</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>6.0.0</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-27 02:33:25</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>715.6799999999999</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Majotr Design Changes on the external design</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>images/HB_01_v5_0_5_20261026112600_sch.png</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.0249,"LC2":0.0223,"LC3":0.10182,"LC4":0.08997,"LC5":0.07444,"LC6":0.06377,"LC7":0.08349,"LC8":0.0222,"LC9":0.0222}</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/HB_01_v6_0_0_LC1_20261027023325.png", "LC2": "images/HB_01_v6_0_0_LC2_20261027023325.png", "LC3": "images/HB_01_v6_0_0_LC3_20261027023325.png", "LC4": "images/HB_01_v6_0_0_LC4_20261027023325.png", "LC5": "images/HB_01_v6_0_0_LC5_20261027023325.png", "LC6": "images/HB_01_v6_0_0_LC6_20261027023325.png", "LC7": "images/HB_01_v6_0_0_LC7_20261027023325.png"}</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>6.0.1</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:47:51</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>715.6799999999999</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Majotr Design Changes on the external design</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>images/HB_01_v5_0_5_20261026112600_sch.png</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.0249,"LC2":0.0223,"LC3":0.25434,"LC4":0.18666,"LC5":0.15404,"LC6":0.06377,"LC7":0.08349,"LC8":0.05762,"LC9":0.05762}</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":"images/HB_01_v6_0_0_LC1_20261027023325.png","LC2":"images/HB_01_v6_0_0_LC2_20261027023325.png","LC3":"images/HB_01_v6_0_1_LC3_20261027184751.png","LC4":"images/HB_01_v6_0_1_LC4_20261027184751.png","LC5":"images/HB_01_v6_0_1_LC5_20261027184751.png","LC6":"images/HB_01_v6_0_0_LC6_20261027023325.png","LC7":"images/HB_01_v6_0_0_LC7_20261027023325.png","LC8":"images/HB_01_v6_0_1_LC8_20261027184751.png","LC9":"images/HB_01_v6_0_1_LC9_20261027184751.png"}</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>6.0.3</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:02:02</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>559.22</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Majotr Design Changes on the external design</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.03801,"LC2":0.0243,"LC3":0.13112,"LC4":0.0958,"LC5":0.07896,"LC6":0.06876,"LC7":0.08989,"LC8":0.02691,"LC9":0.02691}</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":"images/HB_01_v6_0_3_LC1_20261028153920.png","LC2":"images/HB_01_v6_0_3_LC2_20261028153920.png","LC3":"images/HB_01_v6_0_3_LC3_20261027190202.png","LC4":"images/HB_01_v6_0_3_LC4_20261028153920.png","LC5":"images/HB_01_v6_0_3_LC5_20261028153920.png","LC6":"images/HB_01_v6_0_3_LC6_20261028153920.png","LC7":"images/HB_01_v6_0_3_LC7_20261028153920.png","LC8":"images/HB_01_v6_0_3_LC8_20261027190202.png","LC9":"images/HB_01_v6_0_1_LC9_20261027184751.png"}</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>6.2.0</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-29 01:21:31</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>587.17</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Design changes compared 6.0.4 and corrected minimal various things</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.02822,"LC2":0.02553,"LC3":0.10801,"LC4":0.0798,"LC5":0.06615,"LC6":0.05572,"LC7":0.07281,"LC8":0.02483,"LC9":0.02483}</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/HB_01_v6_2_0_LC1_20261029012131.png", "LC2": "images/HB_01_v6_2_0_LC2_20261029012841.png", "LC3": "images/HB_01_v6_2_0_LC3_20261029012131.png", "LC4": "images/HB_01_v6_2_0_LC4_20261029012131.png", "LC5": "images/HB_01_v6_2_0_LC5_20261029012131.png", "LC6": "images/HB_01_v6_2_0_LC6_20261029012841.png", "LC7": "images/HB_01_v6_2_0_LC7_20261029012841.png", "LC8": "images/HB_01_v6_2_0_LC8.png", "LC9": "images/HB_01_v6_2_0_LC9.png"}</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>6.2.1</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-29 02:33:36</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>573.63</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Changed the angle of the hub lid bolts to be th esame as the ribs and maked the otimization of the back rib bigger</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>["images/HB_01_v6_2_1_20261029023340_sch.png","images/HB_01_v6_2_1_20261029024033_1.png"]</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.03212,"LC2":0.02511,"LC3":0.10572,"LC4":0.06487,"LC5":0.06446,"LC6":0.05633,"LC7":0.07286,"LC8":0.02394,"LC9":0.02394}</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/HB_01_v6_2_1_LC1.png", "LC2": "images/HB_01_v6_2_1_LC2_20261029024315.png", "LC3": "images/HB_01_v6_2_1_LC3_20261029023337.png", "LC4": "images/HB_01_v6_2_1_LC4_20261029024315.png", "LC5": "images/HB_01_v6_2_1_LC5_20261029024315.png", "LC6": "images/HB_01_v6_2_1_LC6_20261029024315.png", "LC7": "images/HB_01_v6_2_1_LC7_20261029024315.png", "LC8": "images/HB_01_v6_2_1_LC8_20261029024315.png", "LC9": "images/HB_01_v6_2_1_LC9_20261029024315.png"}</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>6.2.2</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:22:54</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>512.3200000000001</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-Upper Ribs the same
+-Bigger Slot in the lower Rib
+-minimal changes and clean up</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>["images/HB_01_v6_2_2_20261030234723_sch1.png","images/HB_01_v6_2_2_20261030234723_sch2.png","images/HB_01_v6_2_2_20261030234723_sch3.png"]</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.03468,"LC2":0.02964,"LC3":0.14129,"LC4":0.10337,"LC5":0.0852,"LC6":0.07376,"LC7":0.09655,"LC8":0.03377,"LC9":0.03377}</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":"images/HB_01_v6_2_2_LC1_20261030234723.png","LC2":"images/HB_01_v6_2_2_LC2_20261030235251.png","LC3":"images/HB_01_v6_2_2_LC3_20261030234723.png","LC4":"images/HB_01_v6_2_2_LC4_20261030234723.png","LC5":"images/HB_01_v6_2_2_LC5_20261030234723.png","LC6":"images/HB_01_v6_2_2_LC6_20261030235251.png","LC7":"images/HB_01_v6_2_2_LC7_20261030235251.png","LC8":"images/HB_01_v6_2_2_LC8_20261030234723.png","LC9":"images/HB_01_v6_2_2_LC9_20261030234723.png"}</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>6.2.3</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-31 00:00:24</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>516.52</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>-The offset of the backrib cut went back to the 4mm
+-The back ribs distances passed to 3-6-3</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>["images/HB_01_v6_2_3_20261031000024_sch1.png","images/HB_01_v6_2_3_20261031000024_sch2.png","images/HB_01_v6_2_3_20261031000024_sch3.png"]</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.03367,"LC2":0.02907,"LC3":0.14285,"LC4":0.10446,"LC5":0.08609,"LC6":0.07471,"LC7":0.09771,"LC8":0.03164,"LC9":0.03164}</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>{"LC8":"images/HB_01_v6_2_3_LC8_20261031001220.png","LC9":"images/HB_01_v6_2_3_LC9_20261031001220.png","LC3":"images/HB_01_v6_2_3_LC3_20261031001220.png","LC1":"images/HB_01_v6_2_3_LC1_20261031001554.png","LC4":"images/HB_01_v6_2_3_LC4_20261031001554.png","LC5":"images/HB_01_v6_2_3_LC5_20261031001554.png","LC2":"images/HB_01_v6_2_3_LC2_20261031001554.png","LC6":"images/HB_01_v6_2_3_LC6_20261031001554.png","LC7":"images/HB_01_v6_2_3_LC7_20261031001554.png"}</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>6.2.4</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-31 11:07:42</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>515.9400000000001</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>The slot offset on the backribs back to 4mm
+BackRib ribs 2-6-2</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>["images/HB_01_v6_2_4_20261031110742_sch1.png","images/HB_01_v6_2_4_20261031110742_sch2.png","images/HB_01_v6_2_4_20261031110742_sch3.png"]</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.03501,"LC2":0.02868,"LC3":0.15311,"LC4":0.11198,"LC5":0.09226,"LC6":0.07996,"LC7":0.10469,"LC8":0.03509,"LC9":0.03509}</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>{"LC3":"images/HB_01_v6_2_4_LC3_20261031110742.png","LC4":"images/HB_01_v6_2_4_LC4_20261031110742.png","LC5":"images/HB_01_v6_2_4_LC5_20261031110742.png","LC8":"images/HB_01_v6_2_4_LC8_20261031110742.png","LC9":"images/HB_01_v6_2_4_LC9_20261031110742.png","LC1":"images/HB_01_v6_2_4_LC1_20261031110742.png","LC2":"images/HB_01_v6_2_4_LC2_20261031110742.png","LC6":"images/HB_01_v6_2_4_LC6_20261031110742.png","LC7":"images/HB_01_v6_2_4_LC7_20261031110742.png"}</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>HB_01</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>6.2.5</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-31 12:51:16</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>527.28</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>BackRibs: 3-9-3
+BrakeDisc 116
+The rest the same</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>["images/HB_01_v6_2_5_20261031125116_sch1.png","images/HB_01_v6_2_5_20261031125116_sch2.png","images/HB_01_v6_2_5_20261031125116_sch3.png"]</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.02762,"LC2":0.02279,"LC3":0.13809,"LC4":0.1009,"LC5":0.08315,"LC6":0.07224,"LC7":0.09444,"LC8":0.02945,"LC9":0.02945}</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>{"LC3":"images/HB_01_v6_2_5_LC3_20261031130257.png","LC4":"images/HB_01_v6_2_5_LC4_20261031130257.png","LC5":"images/HB_01_v6_2_5_LC5_20261031130257.png","LC8":"images/HB_01_v6_2_5_LC8_20261031130257.png","LC9":"images/HB_01_v6_2_5_LC9_20261031130257.png","LC1":"images/HB_01_v6_2_5_LC1_20261031130257.png","LC2":"images/HB_01_v6_2_5_LC2_20261031130257.png","LC6":"images/HB_01_v6_2_5_LC6_20261031130257.png","LC7":"images/HB_01_v6_2_5_LC7_20261031130257.png"}</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>HB_02</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:28:41</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>HB_07</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:44:16</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2mm to ensure no contact between the bearing and the seal</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>images\HB_07_v1_0_imagem.png</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>61815</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E25" s="1" t="n">
         <v>149</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61815
 Datasheet: 61815</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 75 | Dynamic Load Cr (kN): 13.7 | Static Load C0r (kN): 13.4 | Speed Limit (rpm): 10000</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>61816</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E26" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Deep Groove Ball Bearing 61816 (80x100x10 mm). Datasheet: 61816.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>d (Bore diameter): 80 mm
 D (Outside diameter): 100 mm
@@ -1005,88 +1683,88 @@
 f0 (Calculation factor): 16</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>images/61816_vOEM_20261017_103218.png</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>71815-TN</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E27" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 71815-TN
 Datasheet: 71815</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 75 | Dynamic Load Cr (kN): 16.2 | Static Load C0r (kN): 18.1 | Speed Limit (rpm): 8500</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr">
         <is>
           <t>71816-TN</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D28" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E28" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Schaeffler Bearing: 71816-TN
 Datasheet: https://medias.schaeffler.es/pt/produto/rotary/rolamentos%2c-mancais-de-deslizamento/rolamentos-de-esferas/rolamentos-de-esferas-de-contacto-angular/71816-tn/p/359213?redirect=true </t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>d (Bore diameter): 80 mm
 D (Outside diameter): 100 mm
@@ -1112,52 +1790,52 @@
 Tmax (Max. operating temp): 120 deg C</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>images/71816-TN_vOEM_20261017_175026.png</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>85X100X9 HMSA10 V</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D29" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E29" s="1" t="n">
         <v>43.8</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 85X100X9 HMSA10 V
 Datasheet: https://www.skf.com/pt/products/industrial-seals/power-transmission-seals/radial-shaft-seals/general-industrial-applications/productid-85X100X9%20HMSA10%20V
 </t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>d1 (Shaft diameter): 85 mm
 D (Housing bore diameter): 100 mm
@@ -1173,19 +1851,19 @@
 Max Pressure Difference: 0.05 N/mm2</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>images/85X100X9 HMSA10 V_vOEM_20261017_104022.png</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>### Radial Shaft Seal Analysis &amp; Selection (SKF HMSA10 V)
 In-wheel drivetrain design, the radial shaft seal forms the sealing barrier between the rotating wheel hub and the stationary upright.
@@ -1298,46 +1976,46 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>95X110X9 HMSA10 V</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:00:06</t>
         </is>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E30" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 95X110X9 HMSA10 V
 Datasheet: 95X110X9 </t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 95 | Outer D Min (mm): 110 | Width Min (mm): 9</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>### Radial Shaft Seal Analysis &amp; Selection (SKF HMSA10 V)
 In-wheel drivetrain design, the radial shaft seal forms the sealing barrier between the rotating wheel hub and the stationary upright.
@@ -1450,1493 +2128,1546 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E31" s="1" t="n">
         <v>1049.81</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">To make a baseline </t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_vFST15_20261014_003807.png</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1758, "LC2": 0.2702, "LC3": 0.3631, "LC4": 0.285, "LC5": 0.2541, "LC6": 0.3201, "LC7": 0.3598, "LC8": 0.0835, "LC9": 0.0835}</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>2026-10-12 15:56:06</t>
         </is>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E32" s="1" t="n">
         <v>973.05</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The new upper support design
 </t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Transmission: v1.2
 UpperSuport: v1.0</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.3429, "LC2": 0.3914, "LC3": 0.7797, "LC4": 0.5463, "LC5": 0.4658, "LC6": 0.6519, "LC7": 0.7425, "LC8": 0.1437, "LC9": 0.1437}</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>2026-10-12 16:58:21</t>
         </is>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E33" s="1" t="n">
         <v>996.61</v>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Maked the side walls solid</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Transmission: v1.2
 UpperSuport: v1.0</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.2032, "LC2": 0.2119, "LC3": 0.4325, "LC4": 0.331, "LC5": 0.2905, "LC6": 0.3288, "LC7": 0.3826, "LC8": 0.0883, "LC9": 0.0883}</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B34" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>2.0 (without supports)</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D34" s="1" t="inlineStr">
         <is>
           <t>2026-10-13 20:33:44</t>
         </is>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E34" s="1" t="n">
         <v>532.01</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>For comparing weight before adding the suspension supports with the FST15 design</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v2_0 (without supports)_20261013_203344.png</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.0, "LC2": 0.0, "LC3": 0.0, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0, "LC9": 0.0}</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>FST15 (without supports)</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t>2026-10-13 20:35:55</t>
         </is>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E35" s="1" t="n">
         <v>677.2</v>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>To make a baseline without the supports but with otimization of the transmission area</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Transmission: vFST15</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_vFST15 (without supports)_20261013_203555.png</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.0, "LC2": 0.0, "LC3": 0.0, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0, "LC9": 0.0}</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B36" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D36" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 00:25:37</t>
         </is>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E36" s="1" t="n">
         <v>1029.86</v>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">To make a baseline </t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v2_0_20261014_002537.png</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.2451, "LC2": 0.231, "LC3": 0.4058, "LC4": 0.2989, "LC5": 0.2604, "LC6": 0.3203, "LC7": 0.367, "LC8": 0.0841, "LC9": 0.0841}</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>2.0.1</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 01:22:40</t>
         </is>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E37" s="1" t="n">
         <v>1029.86</v>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">To make a baseline </t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1594, "LC2": 0.2208, "LC3": 0.4183, "LC4": 0.3058, "LC5": 0.2652, "LC6": 0.322, "LC7": 0.3708, "LC8": 0.0849, "LC9": 0.0849}</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 11:33:53</t>
         </is>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E38" s="1" t="n">
         <v>1029.86</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>same supports as v2.0 but with bigger fillets in the pillars</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v2_1_20261014_113714.png</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1469, "LC2": 0.1923, "LC3": 0.3673, "LC4": 0.275, "LC5": 0.2377, "LC6": 0.2701, "LC7": 0.3129, "LC8": 0.0801, "LC9": 0.0801}</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 19:16:18</t>
         </is>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E39" s="1" t="n">
         <v>1022.6</v>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>New try for the pillars and simpler uppersupports of v2.0</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_0_20261014_191617.png</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1597, "LC2": 0.2183, "LC3": 0.4255, "LC4": 0.3094, "LC5": 0.2667, "LC6": 0.3255, "LC7": 0.3747, "LC8": 0.0881, "LC9": 0.0881}</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_0_LC1_20261014_191617.png", "LC2": "images/UP_01_v3_0_LC2_20261014_191617.png", "LC3": "images/UP_01_v3_0_LC3_20261014_191617.png", "LC8": "images/UP_01_v3_0_LC8_20261014_191617.png", "LC4": "images/UP_01_v3_0_LC4_20261014_192056.png", "LC5": "images/UP_01_v3_0_LC5_20261014_192056.png", "LC6": "images/UP_01_v3_0_LC6_20261014_192056.png", "LC7": "images/UP_01_v3_0_LC7_20261014_192056.png"}</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D40" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 10:25:28</t>
         </is>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E40" s="1" t="n">
         <v>1153.17</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Bigger fillets on the pillars</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_1_20261015_102528.png</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1248, "LC2": 0.1625, "LC3": 0.3052, "LC4": 0.2234, "LC5": 0.1917, "LC6": 0.2315, "LC7": 0.2664, "LC8": 0.0648, "LC9": 0.0648}</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_1_LC1_20261015_103709.png", "LC2": "images/UP_01_v3_1_LC2_20261015_103709.png", "LC3": "images/UP_01_v3_1_LC3_20261015_103709.png", "LC4": "images/UP_01_v3_1_LC4_20261015_103710.png", "LC5": "images/UP_01_v3_1_LC5_20261015_103710.png", "LC6": "images/UP_01_v3_1_LC6_20261015_103710.png", "LC7": "images/UP_01_v3_1_LC7_20261015_103710.png", "LC8": "images/UP_01_v3_1_LC8_20261015_103710.png", "LC9": "images/UP_01_v3_1_LC9_20261015_103710.png"}</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>FST15 (1 body)</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 10:30:42</t>
         </is>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E41" s="1" t="n">
         <v>1170.2</v>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>The baseline with one body. The fastest way to iterate</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Transmission: vFST15
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_vFST15 (1 body)_20261015_103042.png</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1664, "LC2": 0.2509, "LC3": 0.3437, "LC4": 0.2647, "LC5": 0.2364, "LC6": 0.2997, "LC7": 0.3382, "LC8": 0.076, "LC9": 0.076}</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_vFST15 (1 body)_LC1_20261015_103042.png", "LC2": "images/UP_01_vFST15 (1 body)_LC2_20261015_103042.png", "LC3": "images/UP_01_vFST15 (1 body)_LC3_20261015_103042.png", "LC4": "images/UP_01_vFST15 (1 body)_LC4_20261015_103042.png", "LC5": "images/UP_01_vFST15 (1 body)_LC5_20261015_103042.png", "LC6": "images/UP_01_vFST15 (1 body)_LC6_20261015_103042.png", "LC7": "images/UP_01_vFST15 (1 body)_LC7_20261015_103042.png", "LC8": "images/UP_01_vFST15 (1 body)_LC8_20261015_103042.png", "LC9": "images/UP_01_vFST15 (1 body)_LC9_20261015_103042.png"}</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>2.0 (1 body)</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D42" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 10:51:55</t>
         </is>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E42" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Sanity Check on the baseline
 </t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v2_0 (1 body)_20261015_105155.png</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1484, "LC2": 0.2071, "LC3": 0.3885, "LC4": 0.2854, "LC5": 0.2487, "LC6": 0.2998, "LC7": 0.3459, "LC8": 0.0788, "LC9": 0.0788}</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>3.1 (without supports)</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 11:17:35</t>
         </is>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E43" s="1" t="n">
         <v>693.88</v>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">For comparison without supports with FST15
 </t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_1 (without supports)_20261015_111735.png</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1484, "LC2": 0.2071, "LC3": 0.3885, "LC4": 0.2854, "LC5": 0.2487, "LC6": 0.2998, "LC7": 0.3459, "LC8": 0.0788, "LC9": 0.0788}</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 11:54:58</t>
         </is>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E44" s="1" t="n">
         <v>1149.1</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Smaller fillet on the upright
 </t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_2_20261015_115458.png</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1311, "LC2": 0.1734, "LC3": 0.3176, "LC4": 0.2332, "LC5": 0.2011, "LC6": 0.2437, "LC7": 0.2799, "LC8": 0.0669, "LC9": 0.0669}</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_2_LC1_20261015_115458.png", "LC2": "images/UP_01_v3_2_LC2_20261015_115458.png", "LC3": "images/UP_01_v3_2_LC3_20261015_115458.png", "LC4": "images/UP_01_v3_2_LC4_20261015_115458.png", "LC5": "images/UP_01_v3_2_LC5_20261015_115458.png", "LC6": "images/UP_01_v3_2_LC6_20261015_115458.png", "LC7": "images/UP_01_v3_2_LC7_20261015_115458.png", "LC8": "images/UP_01_v3_2_LC8_20261015_115746.png", "LC9": "images/UP_01_v3_2_LC9_20261015_115746.png"}</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 16:05:42</t>
         </is>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E45" s="1" t="n">
         <v>1145.42</v>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Make sure the clearences were obtained and had to reduce the fillets on the upright
 </t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_3_20261015_160541.png</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1443, "LC2": 0.1952, "LC3": 0.3579, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0738, "LC9": 0.0738}</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_3_LC1_20261015_160541.png", "LC2": "images/UP_01_v3_3_LC2_20261015_160541.png", "LC3": "images/UP_01_v3_3_LC3_20261015_160541.png", "LC8": "images/UP_01_v3_3_LC8_20261015_160541.png", "LC9": "images/UP_01_v3_3_LC9_20261015_160542.png"}</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t>2026-10-15 16:26:11</t>
         </is>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E46" s="1" t="n">
         <v>1146.28</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The 3.3 didint give the results i wanted so i changed a bit the low fillet to see if improves stiffness
 </t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v3_3_1_20261015_162611.png</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1429, "LC2": 0.1936, "LC3": 0.3532, "LC4": 0.2577, "LC5": 0.2236, "LC6": 0.2743, "LC7": 0.3151, "LC8": 0.0728, "LC9": 0.0738}</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v3_3_1_LC1_20261015_162611.png", "LC2": "images/UP_01_v3_3_1_LC2_20261015_162611.png", "LC3": "images/UP_01_v3_3_1_LC3_20261015_162611.png", "LC8": "images/UP_01_v3_3_1_LC8_20261015_162611.png", "LC9": "images/UP_01_v3_3_1_LC9_20261015_162611.png"}</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D47" s="1" t="inlineStr">
         <is>
           <t>2026-10-21 18:44:13</t>
         </is>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E47" s="1" t="n">
         <v>1126.36</v>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Com a ultima transmissão e umas melhorias nos fillets </t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Transmission: v4.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v4_1_20261021_235100.png</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1298, "LC2": 0.1767, "LC3": 0.3163, "LC4": 0.2282, "LC5": 0.1969, "LC6": 0.2444, "LC7": 0.2797, "LC8": 0.0663, "LC9": 0.0663}</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v4_1_LC1_20261021_234909.png", "LC2": "images/UP_01_v4_1_LC2_20261021_234909.png", "LC3": "images/UP_01_v4_1_LC3_20261021_234909.png", "LC8": "images/UP_01_v4_1_LC8_20261021_234909.png", "LC9": "images/UP_01_v4_1_LC9_20261021_234909.png", "LC4": "images/UP_01_v4_1_LC4_20261021_235418.png", "LC5": "images/UP_01_v4_1_LC5_20261021_235418.png", "LC6": "images/UP_01_v4_1_LC6_20261021_235418.png", "LC7": "images/UP_01_v4_1_LC7_20261021_235418.png"}</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B48" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>4.1.1</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>2026-10-23 10:08:37</t>
         </is>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E48" s="1" t="n">
         <v>1120.57</v>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Alterei a espessura da bridge entre pontos de fixação da tampa de 5mm da v4.1 para 3mm</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Transmission: v4.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v4_1_1_20261023_100837.png</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1305, "LC2": 0.1766, "LC3": 0.3191, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0672, "LC9": 0.0672}</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>4.1.2</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>2026-10-23 10:18:00</t>
         </is>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E49" s="1" t="n">
         <v>1120.57</v>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">fiz rasgos na base dos eixos 
 </t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Transmission: v4.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v4_1_2_20261023_114824.png</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.128, "LC2": 0.1725, "LC3": 0.3098, "LC4": 0.2238, "LC5": 0.1927, "LC6": 0.2389, "LC7": 0.2735, "LC8": 0.0653, "LC9": 0.0653}</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v4_1_2_LC1_20261023_105914.png", "LC2": "images/UP_01_v4_1_2_LC2_20261023_105914.png", "LC3": "images/UP_01_v4_1_2_LC3_20261023_105914.png", "LC8": "images/UP_01_v4_1_2_LC8_20261023_103426.png", "LC9": "images/UP_01_v4_1_2_LC9_20261023_103426.png", "LC4": "images/UP_01_v4_1_2_LC4_20261023_104100.png", "LC5": "images/UP_01_v4_1_2_LC5_20261023_104100.png", "LC6": "images/UP_01_v4_1_2_LC6_20261023_104100.png", "LC7": "images/UP_01_v4_1_2_LC7_20261023_105820.png"}</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B50" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="D50" s="1" t="inlineStr">
         <is>
           <t>2026-10-23 11:45:50</t>
         </is>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E50" s="1" t="n">
         <v>1084.68</v>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Alterei a espessura da bridge entre pontos de fixação da tampa de volta a 5mm e corrigi uma clearence
 </t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Transmission: v4.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v4_1_1_20261023_100837.png</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1291, "LC2": 0.1745, "LC3": 0.3177, "LC4": 0.2294, "LC5": 0.1974, "LC6": 0.2435, "LC7": 0.2791, "LC8": 0.0669, "LC9": 0.0669}</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v4_2_LC1_20261023_114550.png", "LC2": "images/UP_01_v4_2_LC2_20261023_114550.png", "LC3": "images/UP_01_v4_2_LC3_20261023_114550.png", "LC4": "images/UP_01_v4_2_LC4_20261023_114550.png", "LC5": "images/UP_01_v4_2_LC5_20261023_114550.png", "LC6": "images/UP_01_v4_2_LC6_20261023_114550.png", "LC7": "images/UP_01_v4_2_LC7_20261023_114550.png", "LC8": "images/UP_01_v4_2_LC8_20261023_114550.png", "LC9": "images/UP_01_v4_2_LC9_20261023_114550.png"}</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B51" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>4.1.3</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D51" s="1" t="inlineStr">
         <is>
           <t>2026-10-23 18:32:48</t>
         </is>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E51" s="1" t="n">
         <v>1136.03</v>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Alterei a espessura da bridge entre pontos de fixação da tampa para 8mm
 </t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>Transmission: v4.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v4_1_3_20261023_183248.png</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1269, "LC2": 0.1716, "LC3": 0.3024, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0637, "LC9": 0.0637}</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v4_1_3_LC1_20261023_183248.png", "LC2": "images/UP_01_v4_1_3_LC2_20261023_183248.png", "LC3": "images/UP_01_v4_1_3_LC3_20261023_183248.png", "LC8": "images/UP_01_v4_1_3_LC8_20261023_183248.png", "LC9": "images/UP_01_v4_1_3_LC9_20261023_183248.png"}</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B52" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>2026-10-23 19:02:10</t>
         </is>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E52" s="1" t="n">
         <v>1129.22</v>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Alterei a altura do pilar, e aumentei o fillet da tampa do portacubo com a tampa
 </t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Transmission: v4.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v4_3_20261024_092135.png</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1323, "LC2": 0.1808, "LC3": 0.3019, "LC4": 0.22, "LC5": 0.1914, "LC6": 0.2409, "LC7": 0.274, "LC8": 0.0632, "LC9": 0.0632}</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v4_3_LC1_20261023_190210.png", "LC2": "images/UP_01_v4_3_LC2_20261023_190210.png", "LC3": "images/UP_01_v4_3_LC3_20261023_190210.png", "LC8": "images/UP_01_v4_3_LC8_20261023_190210.png", "LC9": "images/UP_01_v4_3_LC9_20261023_190210.png", "LC4": "images/UP_01_v4_3_LC4_20261024_091654.png", "LC5": "images/UP_01_v4_3_LC5_20261024_091654.png", "LC6": "images/UP_01_v4_3_LC6_20261024_091654.png", "LC7": "images/UP_01_v4_3_LC7_20261024_091654.png"}</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>4.3.1</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D53" s="1" t="inlineStr">
         <is>
           <t>2026-10-24 10:53:43</t>
         </is>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E53" s="1" t="n">
         <v>1090.66</v>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">USando os pilares ate ao planeta grande (v4.3) criei slots maquinaveis na interface com o motor
 </t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Transmission: v5.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v4_3_1_20261024_105343.png</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1332, "LC2": 0.1834, "LC3": 0.3074, "LC4": 0.2229, "LC5": 0.1938, "LC6": 0.2452, "LC7": 0.2789, "LC8": 0.0641, "LC9": 0.0641}</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v4_3_1_LC1_20261024_105343.png", "LC2": "images/UP_01_v4_3_1_LC2_20261024_105343.png", "LC3": "images/UP_01_v4_3_1_LC3_20261024_105343.png", "LC4": "images/UP_01_v4_3_1_LC4_20261024_105343.png", "LC5": "images/UP_01_v4_3_1_LC5_20261024_105343.png", "LC6": "images/UP_01_v4_3_1_LC6_20261024_105343.png", "LC7": "images/UP_01_v4_3_1_LC7_20261024_105343.png", "LC8": "images/UP_01_v4_3_1_LC8_20261024_105343.png", "LC9": "images/UP_01_v4_3_1_LC9_20261024_105343.png"}</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B54" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>4.3.2</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="D54" s="1" t="inlineStr">
         <is>
           <t>2026-10-24 12:29:29</t>
         </is>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E54" s="1" t="n">
         <v>1098.53</v>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Melhorei a geometria dos pilares no portacubo e melhorei os slots da interface do motor
 </t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Transmission: v5.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v4_3_2_20261024_122929.png</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1304, "LC2": 0.1767, "LC3": 0.2964, "LC4": 0.2159, "LC5": 0.1876, "LC6": 0.2356, "LC7": 0.2682, "LC8": 0.0623, "LC9": 0.0623}</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v4_3_2_LC1_20261024_123906.png", "LC2": "images/UP_01_v4_3_2_LC2_20261024_123907.png", "LC3": "images/UP_01_v4_3_2_LC3_20261024_123907.png", "LC8": "images/UP_01_v4_3_2_LC8_20261024_123907.png", "LC9": "images/UP_01_v4_3_2_LC9_20261024_123907.png", "LC4": "images/UP_01_v4_3_2_LC4_20261024_124535.png", "LC5": "images/UP_01_v4_3_2_LC5_20261024_124535.png", "LC6": "images/UP_01_v4_3_2_LC6_20261024_124535.png", "LC7": "images/UP_01_v4_3_2_LC7_20261024_124535.png"}</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B55" s="1" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="D55" s="1" t="inlineStr">
         <is>
           <t>2026-10-24 17:30:49</t>
         </is>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E55" s="1" t="n">
         <v>1060.69</v>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corte no LowerSupport e aumento da largura do tierod
 </t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Transmission: v5.0
 Bodies: 1</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>images/UP_01_v6_0_20261024_173049.png</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>{"LC1": 0.1536, "LC2": 0.179, "LC3": 0.2967, "LC4": 0.0, "LC5": 0.0, "LC6": 0.0, "LC7": 0.0, "LC8": 0.0648, "LC9": 0.0648}</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>{"LC1": "images/UP_01_v6_0_LC1_20261024_173049.png", "LC2": "images/UP_01_v6_0_LC2_20261024_173049.png", "LC3": "images/UP_01_v6_0_LC3_20261024_173049.png", "LC8": "images/UP_01_v6_0_LC8_20261024_173049.png", "LC9": "images/UP_01_v6_0_LC9_20261024_173049.png"}</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>UP_01</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:06:00</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>974.96</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Major design change</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v5.0
+Bodies: 1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>images/UP_01_v6_0_20261024_173049.png</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":0.1536,"LC2":0.2213,"LC3":0.2832,"LC4":0.2102,"LC5":0.1842,"LC6":0.247,"LC7":0.2745,"LC8":0.0687,"LC9":0.0687}</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1":"images/UP_01_v6_1_LC1_20261027180600.png","LC2":"images/UP_01_v6_1_LC2_20261027180600.png","LC3":"images/UP_01_v6_1_LC3_20261027180600.png","LC8":"images/UP_01_v6_1_LC8_20261027180600.png","LC9":"images/UP_01_v6_1_LC9_20261027180600.png","LC4":"images/UP_01_v6_1_LC4_20261027180600.png","LC5":"images/UP_01_v6_1_LC5_20261027180600.png","LC6":"images/UP_01_v6_1_LC6_20261027180600.png","LC7":"images/UP_01_v6_1_LC7_20261027180600.png"}</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D57" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E57" s="1" t="n">
         <v>114.52</v>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Upright Lid FST15</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>images\UP_02_vFST15_imagem.png</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D58" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 18:49:19</t>
         </is>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E58" s="1" t="n">
         <v>101.15</v>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Due to the less height is lighter</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>images\UP_02_v1_imagem.png</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B59" s="1" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>FST15 (with all features)</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D59" s="1" t="inlineStr">
         <is>
           <t>2026-10-13 20:39:47</t>
         </is>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E59" s="1" t="n">
         <v>120.04</v>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>images/UP_02_vFST15 (with all features)_20261013_203947.png</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
+      <c r="B60" s="1" t="inlineStr">
         <is>
           <t>UP_02</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>2.0 (with all features)</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D60" s="1" t="inlineStr">
         <is>
           <t>2026-10-13 20:48:17</t>
         </is>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E60" s="1" t="n">
         <v>116.27</v>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Corrected dimensions and features</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>images/UP_02_v2_0 (with all features)_20261013_204817.png</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B61" s="1" t="inlineStr">
         <is>
           <t>UP_03</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D61" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 11:18:14</t>
         </is>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E61" s="1" t="n">
         <v>59.37</v>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">To represent the FST15 part
 </t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>images\UP_03_vFST15_imagem.png</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>### Front Plate Trade Study
 #### 1. Summary &amp; Context
@@ -3029,50 +3760,50 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B62" s="1" t="inlineStr">
         <is>
           <t>UP_04</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="D62" s="1" t="inlineStr">
         <is>
           <t>2026-10-17 11:42:38</t>
         </is>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E62" s="1" t="n">
         <v>40.02</v>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Baseline motor back plate iteration for FST15 carry-over.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Radial O-Ring: 
 Axial O-Ring: </t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>images/UP_04_vFST15_20261017_114238.png</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>### Backplate Rationale
 #### Component Trade-Off Study: Back Plate
@@ -3098,6 +3829,65 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>UP_05</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>2024-05-15 12:00:00</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>49.89</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>FST15 baseline Camber Bracket (CNC Al 7075-T6). Connects upper A-arm spherical bearing to upright body.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Material: Al 7075-T6
+Mass: 49.89 g
+Yield Strength: 503 MPa
+Target FoS: &gt;= 1.92</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>["images/UP_05_vFST15_sch.png"]</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": 0.1553, "LC2": 0.4047, "LC3": 0.3986, "LC4": 0.3746, "LC5": 0.3889, "LC6": 0.2887}</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>{"LC1": "images/UP_05_vFST15_LC1.png", "LC2": "images/UP_05_vFST15_LC2.png", "LC3": "images/UP_05_vFST15_LC3.png", "LC4": "images/UP_05_vFST15_LC4.png", "LC5": "images/UP_05_vFST15_LC5.png", "LC6": "images/UP_05_vFST15_LC6.png"}</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>FST15 baseline Camber Bracket FEM assessment from FEM_Report_DT_UP_05_F.pptx.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
